--- a/Wavcor Summary Leads - Feb 4 rev1 FOR JASON TO UPLOAD INTO ODOO TO ASSIGN DEALER.xlsx
+++ b/Wavcor Summary Leads - Feb 4 rev1 FOR JASON TO UPLOAD INTO ODOO TO ASSIGN DEALER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavcor.sharepoint.com/sites/WavcorInternational/Engineering/Software/Lead Tools/wix-odoo-webhook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37783401-E550-C34E-ABFD-87E4B87FF948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{37783401-E550-C34E-ABFD-87E4B87FF948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A10B1C3F-4647-ED45-9D6F-999C5B4F2EBD}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="620" windowWidth="35940" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10977,7 +10977,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10993,6 +10993,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11099,7 +11105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11118,50 +11124,56 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11469,6 +11481,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="53" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="43" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="43"/>
+    <col min="11" max="11" width="18.1640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.6640625" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="57">
@@ -11496,16 +11516,16 @@
       <c r="H1" s="10" t="s">
         <v>2235</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="22" t="s">
         <v>2236</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="22" t="s">
         <v>2237</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="22" t="s">
         <v>2238</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="22" t="s">
         <v>2239</v>
       </c>
       <c r="M1" s="10" t="s">
@@ -11553,14 +11573,14 @@
         <v>2251</v>
       </c>
       <c r="H2" s="11"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="23" t="s">
         <v>2252</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="24" t="s">
         <v>2253</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="23" t="s">
         <v>2254</v>
       </c>
       <c r="M2" s="11"/>
@@ -11600,16 +11620,16 @@
       <c r="H3" s="11" t="s">
         <v>2263</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="23" t="s">
         <v>2264</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="23" t="s">
         <v>2265</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="23" t="s">
         <v>2263</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="25" t="s">
         <v>2266</v>
       </c>
       <c r="M3" s="11" t="s">
@@ -11651,16 +11671,16 @@
       <c r="H4" s="11" t="s">
         <v>2273</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="23" t="s">
         <v>2274</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="23" t="s">
         <v>2275</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="23" t="s">
         <v>2273</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="25" t="s">
         <v>2276</v>
       </c>
       <c r="M4" s="11" t="s">
@@ -11700,14 +11720,14 @@
       <c r="H5" s="11" t="s">
         <v>2283</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="23" t="s">
         <v>2284</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23" t="s">
         <v>2283</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="25" t="s">
         <v>2285</v>
       </c>
       <c r="M5" s="11"/>
@@ -11717,11 +11737,11 @@
       <c r="O5" s="11" t="s">
         <v>2286</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="12" t="s">
         <v>2287</v>
       </c>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
       <c r="S5" s="11" t="s">
         <v>2288</v>
       </c>
@@ -11751,14 +11771,14 @@
       <c r="H6" s="11" t="s">
         <v>2294</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="23" t="s">
         <v>2295</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11" t="s">
+      <c r="J6" s="23"/>
+      <c r="K6" s="23" t="s">
         <v>2294</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="23" t="s">
         <v>2296</v>
       </c>
       <c r="M6" s="11"/>
@@ -11798,16 +11818,16 @@
       <c r="H7" s="11" t="s">
         <v>2302</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="23" t="s">
         <v>2303</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="23" t="s">
         <v>2302</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="25" t="s">
         <v>2305</v>
       </c>
       <c r="M7" s="11"/>
@@ -11815,11 +11835,11 @@
         <v>2255</v>
       </c>
       <c r="O7" s="11"/>
-      <c r="P7" s="13" t="s">
+      <c r="P7" s="12" t="s">
         <v>2306</v>
       </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
       <c r="S7" s="11" t="s">
         <v>2307</v>
       </c>
@@ -11847,14 +11867,14 @@
         <v>2313</v>
       </c>
       <c r="H8" s="11"/>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="23" t="s">
         <v>2314</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="24" t="s">
         <v>2315</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="25" t="s">
         <v>2316</v>
       </c>
       <c r="M8" s="11"/>
@@ -11892,14 +11912,14 @@
       <c r="H9" s="11" t="s">
         <v>2323</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="23" t="s">
         <v>2324</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11" t="s">
+      <c r="J9" s="23"/>
+      <c r="K9" s="23" t="s">
         <v>2323</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="23" t="s">
         <v>2325</v>
       </c>
       <c r="M9" s="11"/>
@@ -11941,16 +11961,16 @@
       <c r="H10" s="11" t="s">
         <v>2333</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="23" t="s">
         <v>2334</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="23" t="s">
         <v>2335</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="23" t="s">
         <v>2336</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="25" t="s">
         <v>2337</v>
       </c>
       <c r="M10" s="11" t="s">
@@ -11994,16 +12014,16 @@
       <c r="H11" s="11" t="s">
         <v>2343</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="23" t="s">
         <v>2334</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="23" t="s">
         <v>2335</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="23" t="s">
         <v>2336</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="25" t="s">
         <v>2337</v>
       </c>
       <c r="M11" s="11" t="s">
@@ -12043,16 +12063,16 @@
       <c r="H12" s="11" t="s">
         <v>2347</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="23" t="s">
         <v>2334</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="23" t="s">
         <v>2335</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="23" t="s">
         <v>2336</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="25" t="s">
         <v>2337</v>
       </c>
       <c r="M12" s="11" t="s">
@@ -12064,11 +12084,11 @@
       <c r="O12" s="11" t="s">
         <v>2348</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="P12" s="12" t="s">
         <v>2349</v>
       </c>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
       <c r="S12" s="11" t="s">
         <v>2350</v>
       </c>
@@ -12096,16 +12116,16 @@
       <c r="H13" s="11" t="s">
         <v>2353</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="23" t="s">
         <v>2334</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="23" t="s">
         <v>2335</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="23" t="s">
         <v>2336</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="25" t="s">
         <v>2337</v>
       </c>
       <c r="M13" s="11" t="s">
@@ -12149,16 +12169,16 @@
       <c r="H14" s="11" t="s">
         <v>2360</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="23" t="s">
         <v>2334</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="23" t="s">
         <v>2335</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="23" t="s">
         <v>2336</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="25" t="s">
         <v>2337</v>
       </c>
       <c r="M14" s="11" t="s">
@@ -12198,16 +12218,16 @@
       <c r="H15" s="11" t="s">
         <v>2364</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="23" t="s">
         <v>2334</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="23" t="s">
         <v>2335</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="23" t="s">
         <v>2336</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="25" t="s">
         <v>2337</v>
       </c>
       <c r="M15" s="11" t="s">
@@ -12247,14 +12267,14 @@
       <c r="H16" s="11" t="s">
         <v>2368</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="23" t="s">
         <v>2369</v>
       </c>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11" t="s">
+      <c r="J16" s="23"/>
+      <c r="K16" s="23" t="s">
         <v>2370</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="25" t="s">
         <v>2371</v>
       </c>
       <c r="M16" s="11"/>
@@ -12264,11 +12284,11 @@
       <c r="O16" s="11" t="s">
         <v>2372</v>
       </c>
-      <c r="P16" s="13" t="s">
+      <c r="P16" s="12" t="s">
         <v>2373</v>
       </c>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
       <c r="S16" s="11" t="s">
         <v>2374</v>
       </c>
@@ -12298,14 +12318,14 @@
       <c r="H17" s="11" t="s">
         <v>2379</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="23" t="s">
         <v>2380</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11" t="s">
+      <c r="J17" s="23"/>
+      <c r="K17" s="23" t="s">
         <v>2381</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="23" t="s">
         <v>2382</v>
       </c>
       <c r="M17" s="11" t="s">
@@ -12347,14 +12367,14 @@
       <c r="H18" s="11" t="s">
         <v>2388</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="23" t="s">
         <v>2389</v>
       </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11" t="s">
+      <c r="J18" s="23"/>
+      <c r="K18" s="23" t="s">
         <v>2388</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="25" t="s">
         <v>2390</v>
       </c>
       <c r="M18" s="11" t="s">
@@ -12394,16 +12414,16 @@
       <c r="H19" s="11" t="s">
         <v>2396</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="23" t="s">
         <v>2397</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="23" t="s">
         <v>2398</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="23" t="s">
         <v>2396</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="L19" s="25" t="s">
         <v>2399</v>
       </c>
       <c r="M19" s="11"/>
@@ -12413,7 +12433,7 @@
       <c r="O19" s="11" t="s">
         <v>2401</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="P19" s="12" t="s">
         <v>2402</v>
       </c>
       <c r="Q19" s="11"/>
@@ -12449,14 +12469,14 @@
       <c r="H20" s="11" t="s">
         <v>2410</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="23" t="s">
         <v>2411</v>
       </c>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11" t="s">
+      <c r="J20" s="23"/>
+      <c r="K20" s="23" t="s">
         <v>2412</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="25" t="s">
         <v>2413</v>
       </c>
       <c r="M20" s="11" t="s">
@@ -12498,14 +12518,14 @@
       <c r="H21" s="11" t="s">
         <v>2419</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="23" t="s">
         <v>2420</v>
       </c>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11" t="s">
+      <c r="J21" s="23"/>
+      <c r="K21" s="23" t="s">
         <v>2421</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="L21" s="25" t="s">
         <v>2422</v>
       </c>
       <c r="M21" s="11" t="s">
@@ -12545,14 +12565,14 @@
       <c r="H22" s="11" t="s">
         <v>2427</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="23" t="s">
         <v>2428</v>
       </c>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11" t="s">
+      <c r="J22" s="23"/>
+      <c r="K22" s="23" t="s">
         <v>2427</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="L22" s="25" t="s">
         <v>2429</v>
       </c>
       <c r="M22" s="11"/>
@@ -12560,11 +12580,11 @@
         <v>2255</v>
       </c>
       <c r="O22" s="11"/>
-      <c r="P22" s="13" t="s">
+      <c r="P22" s="12" t="s">
         <v>2430</v>
       </c>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
       <c r="S22" s="11" t="s">
         <v>2431</v>
       </c>
@@ -12592,14 +12612,14 @@
       <c r="H23" s="11" t="s">
         <v>2435</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="23" t="s">
         <v>2428</v>
       </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11" t="s">
+      <c r="J23" s="23"/>
+      <c r="K23" s="23" t="s">
         <v>2427</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="L23" s="25" t="s">
         <v>2429</v>
       </c>
       <c r="M23" s="11"/>
@@ -12637,14 +12657,14 @@
       <c r="H24" s="11" t="s">
         <v>2442</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="23" t="s">
         <v>2443</v>
       </c>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11" t="s">
+      <c r="J24" s="23"/>
+      <c r="K24" s="23" t="s">
         <v>2444</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="23" t="s">
         <v>2445</v>
       </c>
       <c r="M24" s="11"/>
@@ -12654,11 +12674,11 @@
       <c r="O24" s="11" t="s">
         <v>2446</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="P24" s="12" t="s">
         <v>2447</v>
       </c>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
       <c r="S24" s="11" t="s">
         <v>2448</v>
       </c>
@@ -12686,14 +12706,14 @@
       <c r="H25" s="11" t="s">
         <v>2454</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="23" t="s">
         <v>2455</v>
       </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11" t="s">
+      <c r="J25" s="23"/>
+      <c r="K25" s="23" t="s">
         <v>2456</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="L25" s="25" t="s">
         <v>2457</v>
       </c>
       <c r="M25" s="11"/>
@@ -12731,14 +12751,14 @@
       <c r="H26" s="11" t="s">
         <v>2462</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="23" t="s">
         <v>2455</v>
       </c>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11" t="s">
+      <c r="J26" s="23"/>
+      <c r="K26" s="23" t="s">
         <v>2456</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="L26" s="25" t="s">
         <v>2457</v>
       </c>
       <c r="M26" s="11"/>
@@ -12778,14 +12798,14 @@
       <c r="H27" s="11" t="s">
         <v>2466</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="23" t="s">
         <v>2455</v>
       </c>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11" t="s">
+      <c r="J27" s="23"/>
+      <c r="K27" s="23" t="s">
         <v>2456</v>
       </c>
-      <c r="L27" s="13" t="s">
+      <c r="L27" s="25" t="s">
         <v>2457</v>
       </c>
       <c r="M27" s="11" t="s">
@@ -12825,16 +12845,16 @@
       <c r="H28" s="11" t="s">
         <v>2471</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="23" t="s">
         <v>2472</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="23" t="s">
         <v>2473</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="23" t="s">
         <v>2471</v>
       </c>
-      <c r="L28" s="13" t="s">
+      <c r="L28" s="25" t="s">
         <v>2474</v>
       </c>
       <c r="M28" s="11" t="s">
@@ -12876,14 +12896,14 @@
       <c r="H29" s="11" t="s">
         <v>2480</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="23" t="s">
         <v>2481</v>
       </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11" t="s">
+      <c r="J29" s="23"/>
+      <c r="K29" s="23" t="s">
         <v>2480</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="L29" s="25" t="s">
         <v>2482</v>
       </c>
       <c r="M29" s="11"/>
@@ -12921,16 +12941,16 @@
       <c r="H30" s="11" t="s">
         <v>2487</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="23" t="s">
         <v>2488</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="23" t="s">
         <v>2489</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K30" s="23" t="s">
         <v>2490</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="25" t="s">
         <v>2491</v>
       </c>
       <c r="M30" s="11" t="s">
@@ -12974,16 +12994,16 @@
       <c r="H31" s="11" t="s">
         <v>2500</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="23" t="s">
         <v>2501</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="23" t="s">
         <v>2502</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K31" s="23" t="s">
         <v>2503</v>
       </c>
-      <c r="L31" s="13" t="s">
+      <c r="L31" s="25" t="s">
         <v>2504</v>
       </c>
       <c r="M31" s="11" t="s">
@@ -13017,14 +13037,14 @@
       <c r="H32" s="11" t="s">
         <v>2510</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="23" t="s">
         <v>2511</v>
       </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11" t="s">
+      <c r="J32" s="23"/>
+      <c r="K32" s="23" t="s">
         <v>2510</v>
       </c>
-      <c r="L32" s="13" t="s">
+      <c r="L32" s="25" t="s">
         <v>2512</v>
       </c>
       <c r="M32" s="11"/>
@@ -13062,16 +13082,16 @@
       <c r="H33" s="11" t="s">
         <v>2519</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="23" t="s">
         <v>2520</v>
       </c>
-      <c r="J33" s="11" t="s">
+      <c r="J33" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K33" s="23" t="s">
         <v>2521</v>
       </c>
-      <c r="L33" s="13" t="s">
+      <c r="L33" s="25" t="s">
         <v>2522</v>
       </c>
       <c r="M33" s="11"/>
@@ -13111,16 +13131,16 @@
       <c r="H34" s="11" t="s">
         <v>2521</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="23" t="s">
         <v>2520</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="J34" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="23" t="s">
         <v>2521</v>
       </c>
-      <c r="L34" s="13" t="s">
+      <c r="L34" s="25" t="s">
         <v>2522</v>
       </c>
       <c r="M34" s="11"/>
@@ -13158,16 +13178,16 @@
       <c r="H35" s="11" t="s">
         <v>2533</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="23" t="s">
         <v>2520</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="J35" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K35" s="23" t="s">
         <v>2521</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="L35" s="25" t="s">
         <v>2522</v>
       </c>
       <c r="M35" s="11"/>
@@ -13205,16 +13225,16 @@
       <c r="H36" s="11" t="s">
         <v>2538</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="23" t="s">
         <v>2539</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="J36" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K36" s="23" t="s">
         <v>2538</v>
       </c>
-      <c r="L36" s="13" t="s">
+      <c r="L36" s="25" t="s">
         <v>2540</v>
       </c>
       <c r="M36" s="11"/>
@@ -13252,16 +13272,16 @@
       <c r="H37" s="11" t="s">
         <v>2545</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="23" t="s">
         <v>2546</v>
       </c>
-      <c r="J37" s="11" t="s">
+      <c r="J37" s="23" t="s">
         <v>2547</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="23" t="s">
         <v>2548</v>
       </c>
-      <c r="L37" s="13" t="s">
+      <c r="L37" s="25" t="s">
         <v>2549</v>
       </c>
       <c r="M37" s="11"/>
@@ -13299,16 +13319,16 @@
       <c r="H38" s="11" t="s">
         <v>2553</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="23" t="s">
         <v>2546</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="23" t="s">
         <v>2547</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K38" s="23" t="s">
         <v>2548</v>
       </c>
-      <c r="L38" s="13" t="s">
+      <c r="L38" s="25" t="s">
         <v>2549</v>
       </c>
       <c r="M38" s="11"/>
@@ -13346,16 +13366,16 @@
       <c r="H39" s="11" t="s">
         <v>2558</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="23" t="s">
         <v>2546</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="J39" s="23" t="s">
         <v>2547</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K39" s="23" t="s">
         <v>2548</v>
       </c>
-      <c r="L39" s="13" t="s">
+      <c r="L39" s="25" t="s">
         <v>2549</v>
       </c>
       <c r="M39" s="11"/>
@@ -13395,14 +13415,14 @@
       <c r="H40" s="11" t="s">
         <v>2564</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="23" t="s">
         <v>2565</v>
       </c>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11" t="s">
+      <c r="J40" s="23"/>
+      <c r="K40" s="23" t="s">
         <v>2566</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L40" s="25" t="s">
         <v>2567</v>
       </c>
       <c r="M40" s="11"/>
@@ -13438,14 +13458,14 @@
       <c r="H41" s="11" t="s">
         <v>2573</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="23" t="s">
         <v>2574</v>
       </c>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11" t="s">
+      <c r="J41" s="23"/>
+      <c r="K41" s="23" t="s">
         <v>2573</v>
       </c>
-      <c r="L41" s="13" t="s">
+      <c r="L41" s="25" t="s">
         <v>2575</v>
       </c>
       <c r="M41" s="11" t="s">
@@ -13485,16 +13505,16 @@
       <c r="H42" s="11" t="s">
         <v>2579</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="23" t="s">
         <v>2580</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="23" t="s">
         <v>2265</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K42" s="23" t="s">
         <v>2579</v>
       </c>
-      <c r="L42" s="13" t="s">
+      <c r="L42" s="25" t="s">
         <v>2581</v>
       </c>
       <c r="M42" s="11" t="s">
@@ -13534,16 +13554,16 @@
       <c r="H43" s="11" t="s">
         <v>2586</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="23" t="s">
         <v>2580</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J43" s="23" t="s">
         <v>2265</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="K43" s="23" t="s">
         <v>2579</v>
       </c>
-      <c r="L43" s="13" t="s">
+      <c r="L43" s="25" t="s">
         <v>2581</v>
       </c>
       <c r="M43" s="11" t="s">
@@ -13583,14 +13603,14 @@
       <c r="H44" s="11" t="s">
         <v>2590</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="23" t="s">
         <v>2591</v>
       </c>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11" t="s">
+      <c r="J44" s="23"/>
+      <c r="K44" s="23" t="s">
         <v>2590</v>
       </c>
-      <c r="L44" s="13" t="s">
+      <c r="L44" s="25" t="s">
         <v>2592</v>
       </c>
       <c r="M44" s="11"/>
@@ -13628,14 +13648,14 @@
       <c r="H45" s="11" t="s">
         <v>2597</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="23" t="s">
         <v>2598</v>
       </c>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11" t="s">
+      <c r="J45" s="23"/>
+      <c r="K45" s="23" t="s">
         <v>2597</v>
       </c>
-      <c r="L45" s="13" t="s">
+      <c r="L45" s="25" t="s">
         <v>2599</v>
       </c>
       <c r="M45" s="11"/>
@@ -13673,14 +13693,14 @@
       <c r="H46" s="11" t="s">
         <v>2604</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="23" t="s">
         <v>2598</v>
       </c>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11" t="s">
+      <c r="J46" s="23"/>
+      <c r="K46" s="23" t="s">
         <v>2597</v>
       </c>
-      <c r="L46" s="13" t="s">
+      <c r="L46" s="25" t="s">
         <v>2599</v>
       </c>
       <c r="M46" s="11"/>
@@ -13718,14 +13738,14 @@
       <c r="H47" s="11" t="s">
         <v>2608</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="23" t="s">
         <v>2598</v>
       </c>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11" t="s">
+      <c r="J47" s="23"/>
+      <c r="K47" s="23" t="s">
         <v>2597</v>
       </c>
-      <c r="L47" s="13" t="s">
+      <c r="L47" s="25" t="s">
         <v>2599</v>
       </c>
       <c r="M47" s="11"/>
@@ -13765,16 +13785,16 @@
       <c r="H48" s="11" t="s">
         <v>2613</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="23" t="s">
         <v>2614</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="23" t="s">
         <v>2613</v>
       </c>
-      <c r="L48" s="13" t="s">
+      <c r="L48" s="25" t="s">
         <v>2615</v>
       </c>
       <c r="M48" s="11"/>
@@ -13812,16 +13832,16 @@
       <c r="H49" s="11" t="s">
         <v>2619</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="23" t="s">
         <v>2614</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="23" t="s">
         <v>2613</v>
       </c>
-      <c r="L49" s="13" t="s">
+      <c r="L49" s="25" t="s">
         <v>2615</v>
       </c>
       <c r="M49" s="11"/>
@@ -13861,14 +13881,14 @@
       <c r="H50" s="11" t="s">
         <v>2625</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="23" t="s">
         <v>2626</v>
       </c>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11" t="s">
+      <c r="J50" s="23"/>
+      <c r="K50" s="23" t="s">
         <v>2625</v>
       </c>
-      <c r="L50" s="13" t="s">
+      <c r="L50" s="25" t="s">
         <v>2627</v>
       </c>
       <c r="M50" s="11" t="s">
@@ -13908,14 +13928,14 @@
       <c r="H51" s="11" t="s">
         <v>2632</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11" t="s">
+      <c r="J51" s="23"/>
+      <c r="K51" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L51" s="13" t="s">
+      <c r="L51" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M51" s="11" t="s">
@@ -13928,7 +13948,7 @@
       <c r="P51" s="11"/>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
-      <c r="S51" s="15" t="s">
+      <c r="S51" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -13955,14 +13975,14 @@
       <c r="H52" s="11" t="s">
         <v>2632</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11" t="s">
+      <c r="J52" s="23"/>
+      <c r="K52" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L52" s="13" t="s">
+      <c r="L52" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M52" s="11" t="s">
@@ -13975,7 +13995,7 @@
       <c r="P52" s="11"/>
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
-      <c r="S52" s="15" t="s">
+      <c r="S52" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -14002,14 +14022,14 @@
       <c r="H53" s="11" t="s">
         <v>2643</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11" t="s">
+      <c r="J53" s="23"/>
+      <c r="K53" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L53" s="13" t="s">
+      <c r="L53" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M53" s="11" t="s">
@@ -14022,7 +14042,7 @@
       <c r="P53" s="11"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
-      <c r="S53" s="15" t="s">
+      <c r="S53" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -14049,14 +14069,14 @@
       <c r="H54" s="11" t="s">
         <v>2648</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11" t="s">
+      <c r="J54" s="23"/>
+      <c r="K54" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L54" s="13" t="s">
+      <c r="L54" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M54" s="11" t="s">
@@ -14069,7 +14089,7 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
-      <c r="S54" s="15" t="s">
+      <c r="S54" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -14096,14 +14116,14 @@
       <c r="H55" s="11" t="s">
         <v>2632</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11" t="s">
+      <c r="J55" s="23"/>
+      <c r="K55" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L55" s="13" t="s">
+      <c r="L55" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M55" s="11" t="s">
@@ -14116,7 +14136,7 @@
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
-      <c r="S55" s="15" t="s">
+      <c r="S55" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -14143,14 +14163,14 @@
       <c r="H56" s="11" t="s">
         <v>2632</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11" t="s">
+      <c r="J56" s="23"/>
+      <c r="K56" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L56" s="13" t="s">
+      <c r="L56" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M56" s="11" t="s">
@@ -14160,10 +14180,10 @@
         <v>2255</v>
       </c>
       <c r="O56" s="11"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="15"/>
-      <c r="S56" s="15" t="s">
+      <c r="P56" s="14"/>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -14190,14 +14210,14 @@
       <c r="H57" s="11" t="s">
         <v>2632</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="23" t="s">
         <v>2633</v>
       </c>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11" t="s">
+      <c r="J57" s="23"/>
+      <c r="K57" s="23" t="s">
         <v>2634</v>
       </c>
-      <c r="L57" s="13" t="s">
+      <c r="L57" s="25" t="s">
         <v>2635</v>
       </c>
       <c r="M57" s="11" t="s">
@@ -14210,7 +14230,7 @@
       <c r="P57" s="11"/>
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
-      <c r="S57" s="15" t="s">
+      <c r="S57" s="14" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -14239,16 +14259,16 @@
       <c r="H58" s="11" t="s">
         <v>2663</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="23" t="s">
         <v>2664</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="23" t="s">
         <v>2665</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="23" t="s">
         <v>2666</v>
       </c>
-      <c r="L58" s="13" t="s">
+      <c r="L58" s="25" t="s">
         <v>2667</v>
       </c>
       <c r="M58" s="11" t="s">
@@ -14290,14 +14310,14 @@
       <c r="H59" s="11" t="s">
         <v>2673</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="23" t="s">
         <v>2674</v>
       </c>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11" t="s">
+      <c r="J59" s="23"/>
+      <c r="K59" s="23" t="s">
         <v>2673</v>
       </c>
-      <c r="L59" s="13" t="s">
+      <c r="L59" s="25" t="s">
         <v>2675</v>
       </c>
       <c r="M59" s="11" t="s">
@@ -14313,7 +14333,7 @@
       <c r="Q59" s="11" t="s">
         <v>2677</v>
       </c>
-      <c r="R59" s="14" t="s">
+      <c r="R59" s="13" t="s">
         <v>2678</v>
       </c>
       <c r="S59" s="11" t="s">
@@ -14341,16 +14361,16 @@
       <c r="H60" s="11" t="s">
         <v>2681</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="23" t="s">
         <v>2682</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="23" t="s">
         <v>2683</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="23" t="s">
         <v>2684</v>
       </c>
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="23" t="s">
         <v>2685</v>
       </c>
       <c r="M60" s="11" t="s">
@@ -14362,13 +14382,13 @@
       <c r="O60" s="11" t="s">
         <v>2686</v>
       </c>
-      <c r="P60" s="13" t="s">
+      <c r="P60" s="12" t="s">
         <v>2687</v>
       </c>
       <c r="Q60" s="11" t="s">
         <v>2688</v>
       </c>
-      <c r="R60" s="13" t="s">
+      <c r="R60" s="12" t="s">
         <v>2689</v>
       </c>
       <c r="S60" s="11" t="s">
@@ -14398,16 +14418,16 @@
       <c r="H61" s="11" t="s">
         <v>2693</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="23" t="s">
         <v>2694</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J61" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="K61" s="23" t="s">
         <v>2693</v>
       </c>
-      <c r="L61" s="13" t="s">
+      <c r="L61" s="25" t="s">
         <v>2695</v>
       </c>
       <c r="M61" s="11" t="s">
@@ -14419,11 +14439,11 @@
       <c r="O61" s="11" t="s">
         <v>2677</v>
       </c>
-      <c r="P61" s="14" t="s">
+      <c r="P61" s="13" t="s">
         <v>2678</v>
       </c>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14"/>
+      <c r="Q61" s="13"/>
+      <c r="R61" s="13"/>
       <c r="S61" s="11" t="s">
         <v>2696</v>
       </c>
@@ -14453,16 +14473,16 @@
       <c r="H62" s="11" t="s">
         <v>2700</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="23" t="s">
         <v>2701</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="K62" s="23" t="s">
         <v>2700</v>
       </c>
-      <c r="L62" s="11"/>
+      <c r="L62" s="23"/>
       <c r="M62" s="11" t="s">
         <v>2383</v>
       </c>
@@ -14472,13 +14492,13 @@
       <c r="O62" s="11" t="s">
         <v>2702</v>
       </c>
-      <c r="P62" s="13" t="s">
+      <c r="P62" s="12" t="s">
         <v>2703</v>
       </c>
       <c r="Q62" s="11" t="s">
         <v>2704</v>
       </c>
-      <c r="R62" s="13" t="s">
+      <c r="R62" s="12" t="s">
         <v>2705</v>
       </c>
       <c r="S62" s="11" t="s">
@@ -14510,16 +14530,16 @@
       <c r="H63" s="11" t="s">
         <v>2710</v>
       </c>
-      <c r="I63" s="11" t="s">
+      <c r="I63" s="23" t="s">
         <v>2711</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="J63" s="23" t="s">
         <v>2712</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="K63" s="23" t="s">
         <v>2713</v>
       </c>
-      <c r="L63" s="13" t="s">
+      <c r="L63" s="25" t="s">
         <v>2714</v>
       </c>
       <c r="M63" s="11" t="s">
@@ -14531,11 +14551,11 @@
       <c r="O63" s="11" t="s">
         <v>2715</v>
       </c>
-      <c r="P63" s="13" t="s">
+      <c r="P63" s="12" t="s">
         <v>2716</v>
       </c>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="14"/>
+      <c r="Q63" s="13"/>
+      <c r="R63" s="13"/>
       <c r="S63" s="11" t="s">
         <v>2717</v>
       </c>
@@ -14563,14 +14583,14 @@
       <c r="H64" s="11" t="s">
         <v>2721</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="23" t="s">
         <v>2722</v>
       </c>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11" t="s">
+      <c r="J64" s="23"/>
+      <c r="K64" s="23" t="s">
         <v>2723</v>
       </c>
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="23" t="s">
         <v>2724</v>
       </c>
       <c r="M64" s="11" t="s">
@@ -14612,16 +14632,16 @@
       <c r="H65" s="11" t="s">
         <v>2731</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="23" t="s">
         <v>2732</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="K65" s="23" t="s">
         <v>2733</v>
       </c>
-      <c r="L65" s="13" t="s">
+      <c r="L65" s="25" t="s">
         <v>2734</v>
       </c>
       <c r="M65" s="11"/>
@@ -14661,16 +14681,16 @@
       <c r="H66" s="11" t="s">
         <v>2741</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="23" t="s">
         <v>2742</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="K66" s="23" t="s">
         <v>2743</v>
       </c>
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="23" t="s">
         <v>2744</v>
       </c>
       <c r="M66" s="11" t="s">
@@ -14688,7 +14708,7 @@
       <c r="Q66" s="11" t="s">
         <v>2747</v>
       </c>
-      <c r="R66" s="13" t="s">
+      <c r="R66" s="12" t="s">
         <v>2748</v>
       </c>
       <c r="S66" s="11" t="s">
@@ -14718,16 +14738,16 @@
       <c r="H67" s="11" t="s">
         <v>2754</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="I67" s="23" t="s">
         <v>2742</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J67" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="K67" s="23" t="s">
         <v>2743</v>
       </c>
-      <c r="L67" s="13" t="s">
+      <c r="L67" s="25" t="s">
         <v>2744</v>
       </c>
       <c r="M67" s="11"/>
@@ -14743,7 +14763,7 @@
       <c r="Q67" s="11" t="s">
         <v>2747</v>
       </c>
-      <c r="R67" s="13" t="s">
+      <c r="R67" s="12" t="s">
         <v>2748</v>
       </c>
       <c r="S67" s="11" t="s">
@@ -14773,16 +14793,16 @@
       <c r="H68" s="11" t="s">
         <v>2760</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="23" t="s">
         <v>2761</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="23" t="s">
         <v>2762</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="K68" s="23" t="s">
         <v>2763</v>
       </c>
-      <c r="L68" s="13" t="s">
+      <c r="L68" s="25" t="s">
         <v>2764</v>
       </c>
       <c r="M68" s="11"/>
@@ -14824,16 +14844,16 @@
       <c r="H69" s="11" t="s">
         <v>2771</v>
       </c>
-      <c r="I69" s="11" t="s">
+      <c r="I69" s="23" t="s">
         <v>2761</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J69" s="23" t="s">
         <v>2762</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="23" t="s">
         <v>2763</v>
       </c>
-      <c r="L69" s="13" t="s">
+      <c r="L69" s="25" t="s">
         <v>2764</v>
       </c>
       <c r="M69" s="11"/>
@@ -14843,11 +14863,11 @@
       <c r="O69" s="11" t="s">
         <v>2765</v>
       </c>
-      <c r="P69" s="13" t="s">
+      <c r="P69" s="12" t="s">
         <v>2766</v>
       </c>
-      <c r="Q69" s="14"/>
-      <c r="R69" s="14"/>
+      <c r="Q69" s="13"/>
+      <c r="R69" s="13"/>
       <c r="S69" s="11" t="s">
         <v>2772</v>
       </c>
@@ -14877,16 +14897,16 @@
       <c r="H70" s="11" t="s">
         <v>2777</v>
       </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="23" t="s">
         <v>2761</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="23" t="s">
         <v>2762</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K70" s="23" t="s">
         <v>2763</v>
       </c>
-      <c r="L70" s="13" t="s">
+      <c r="L70" s="25" t="s">
         <v>2764</v>
       </c>
       <c r="M70" s="11"/>
@@ -14926,16 +14946,16 @@
       <c r="H71" s="11" t="s">
         <v>2780</v>
       </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="23" t="s">
         <v>2761</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="23" t="s">
         <v>2762</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K71" s="23" t="s">
         <v>2763</v>
       </c>
-      <c r="L71" s="13" t="s">
+      <c r="L71" s="25" t="s">
         <v>2764</v>
       </c>
       <c r="M71" s="11"/>
@@ -14945,11 +14965,11 @@
       <c r="O71" s="11" t="s">
         <v>2765</v>
       </c>
-      <c r="P71" s="13" t="s">
+      <c r="P71" s="12" t="s">
         <v>2766</v>
       </c>
-      <c r="Q71" s="14"/>
-      <c r="R71" s="14"/>
+      <c r="Q71" s="13"/>
+      <c r="R71" s="13"/>
       <c r="S71" s="11" t="s">
         <v>2781</v>
       </c>
@@ -14977,14 +14997,14 @@
       <c r="H72" s="11" t="s">
         <v>2786</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="23" t="s">
         <v>2787</v>
       </c>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11" t="s">
+      <c r="J72" s="23"/>
+      <c r="K72" s="23" t="s">
         <v>2786</v>
       </c>
-      <c r="L72" s="13" t="s">
+      <c r="L72" s="25" t="s">
         <v>2788</v>
       </c>
       <c r="M72" s="11"/>
@@ -15022,14 +15042,14 @@
       <c r="H73" s="11" t="s">
         <v>2794</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="23" t="s">
         <v>2795</v>
       </c>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11" t="s">
+      <c r="J73" s="23"/>
+      <c r="K73" s="23" t="s">
         <v>2794</v>
       </c>
-      <c r="L73" s="13" t="s">
+      <c r="L73" s="25" t="s">
         <v>2796</v>
       </c>
       <c r="M73" s="11" t="s">
@@ -15069,14 +15089,14 @@
       <c r="H74" s="11" t="s">
         <v>2800</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="23" t="s">
         <v>2801</v>
       </c>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11" t="s">
+      <c r="J74" s="23"/>
+      <c r="K74" s="23" t="s">
         <v>2802</v>
       </c>
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="23" t="s">
         <v>2803</v>
       </c>
       <c r="M74" s="11" t="s">
@@ -15116,14 +15136,14 @@
       <c r="H75" s="11" t="s">
         <v>2808</v>
       </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="23" t="s">
         <v>2801</v>
       </c>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11" t="s">
+      <c r="J75" s="23"/>
+      <c r="K75" s="23" t="s">
         <v>2802</v>
       </c>
-      <c r="L75" s="11" t="s">
+      <c r="L75" s="23" t="s">
         <v>2803</v>
       </c>
       <c r="M75" s="11" t="s">
@@ -15135,7 +15155,7 @@
       <c r="O75" s="11" t="s">
         <v>2809</v>
       </c>
-      <c r="P75" s="13" t="s">
+      <c r="P75" s="12" t="s">
         <v>2810</v>
       </c>
       <c r="Q75" s="11" t="s">
@@ -15171,14 +15191,14 @@
       <c r="H76" s="11" t="s">
         <v>2818</v>
       </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="23" t="s">
         <v>2801</v>
       </c>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11" t="s">
+      <c r="J76" s="23"/>
+      <c r="K76" s="23" t="s">
         <v>2802</v>
       </c>
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="23" t="s">
         <v>2803</v>
       </c>
       <c r="M76" s="11" t="s">
@@ -15216,16 +15236,16 @@
       <c r="H77" s="11" t="s">
         <v>2822</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="23" t="s">
         <v>2823</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J77" s="23" t="s">
         <v>2824</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="23" t="s">
         <v>2822</v>
       </c>
-      <c r="L77" s="13" t="s">
+      <c r="L77" s="25" t="s">
         <v>2825</v>
       </c>
       <c r="M77" s="11" t="s">
@@ -15237,11 +15257,11 @@
       <c r="O77" s="11" t="s">
         <v>2826</v>
       </c>
-      <c r="P77" s="13" t="s">
+      <c r="P77" s="12" t="s">
         <v>2827</v>
       </c>
-      <c r="Q77" s="14"/>
-      <c r="R77" s="14"/>
+      <c r="Q77" s="13"/>
+      <c r="R77" s="13"/>
       <c r="S77" s="11" t="s">
         <v>2828</v>
       </c>
@@ -15271,14 +15291,14 @@
       <c r="H78" s="11" t="s">
         <v>2833</v>
       </c>
-      <c r="I78" s="13" t="s">
+      <c r="I78" s="25" t="s">
         <v>2834</v>
       </c>
-      <c r="J78" s="14"/>
-      <c r="K78" s="11" t="s">
+      <c r="J78" s="26"/>
+      <c r="K78" s="23" t="s">
         <v>2835</v>
       </c>
-      <c r="L78" s="13" t="s">
+      <c r="L78" s="25" t="s">
         <v>2836</v>
       </c>
       <c r="M78" s="11"/>
@@ -15316,17 +15336,17 @@
       <c r="H79" s="11" t="s">
         <v>2840</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="23" t="s">
         <v>2841</v>
       </c>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11" t="s">
+      <c r="J79" s="23"/>
+      <c r="K79" s="23" t="s">
         <v>2842</v>
       </c>
-      <c r="L79" s="13" t="s">
+      <c r="L79" s="25" t="s">
         <v>2843</v>
       </c>
-      <c r="M79" s="14"/>
+      <c r="M79" s="13"/>
       <c r="N79" s="11" t="s">
         <v>2255</v>
       </c>
@@ -15361,14 +15381,14 @@
       <c r="H80" s="11" t="s">
         <v>2848</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="23" t="s">
         <v>2849</v>
       </c>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11" t="s">
+      <c r="J80" s="23"/>
+      <c r="K80" s="23" t="s">
         <v>2848</v>
       </c>
-      <c r="L80" s="13" t="s">
+      <c r="L80" s="25" t="s">
         <v>2850</v>
       </c>
       <c r="M80" s="11"/>
@@ -15406,19 +15426,19 @@
       <c r="H81" s="11" t="s">
         <v>2855</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="23" t="s">
         <v>2856</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="23" t="s">
         <v>2857</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="23" t="s">
         <v>2858</v>
       </c>
-      <c r="L81" s="13" t="s">
+      <c r="L81" s="25" t="s">
         <v>2859</v>
       </c>
-      <c r="M81" s="14"/>
+      <c r="M81" s="13"/>
       <c r="N81" s="11" t="s">
         <v>2255</v>
       </c>
@@ -15453,19 +15473,19 @@
       <c r="H82" s="11" t="s">
         <v>2858</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="23" t="s">
         <v>2856</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="23" t="s">
         <v>2857</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="23" t="s">
         <v>2858</v>
       </c>
-      <c r="L82" s="13" t="s">
+      <c r="L82" s="25" t="s">
         <v>2859</v>
       </c>
-      <c r="M82" s="14"/>
+      <c r="M82" s="13"/>
       <c r="N82" s="11" t="s">
         <v>2255</v>
       </c>
@@ -15502,16 +15522,16 @@
       <c r="H83" s="11" t="s">
         <v>2868</v>
       </c>
-      <c r="I83" s="11" t="s">
+      <c r="I83" s="23" t="s">
         <v>2869</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="J83" s="23" t="s">
         <v>2870</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="23" t="s">
         <v>2871</v>
       </c>
-      <c r="L83" s="13" t="s">
+      <c r="L83" s="25" t="s">
         <v>2872</v>
       </c>
       <c r="M83" s="11" t="s">
@@ -15547,14 +15567,14 @@
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="23" t="s">
         <v>2878</v>
       </c>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11" t="s">
+      <c r="J84" s="23"/>
+      <c r="K84" s="23" t="s">
         <v>2879</v>
       </c>
-      <c r="L84" s="14" t="s">
+      <c r="L84" s="26" t="s">
         <v>2880</v>
       </c>
       <c r="M84" s="11"/>
@@ -15594,14 +15614,14 @@
       <c r="H85" s="11" t="s">
         <v>2886</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="23" t="s">
         <v>2887</v>
       </c>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11" t="s">
+      <c r="J85" s="23"/>
+      <c r="K85" s="23" t="s">
         <v>2888</v>
       </c>
-      <c r="L85" s="11" t="s">
+      <c r="L85" s="23" t="s">
         <v>2889</v>
       </c>
       <c r="M85" s="11"/>
@@ -15639,16 +15659,16 @@
       <c r="H86" s="11" t="s">
         <v>2895</v>
       </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="23" t="s">
         <v>2896</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="23" t="s">
         <v>2897</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="23" t="s">
         <v>2895</v>
       </c>
-      <c r="L86" s="13" t="s">
+      <c r="L86" s="25" t="s">
         <v>2898</v>
       </c>
       <c r="M86" s="11"/>
@@ -15686,16 +15706,16 @@
       <c r="H87" s="11" t="s">
         <v>2903</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="23" t="s">
         <v>2904</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="J87" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="23" t="s">
         <v>2903</v>
       </c>
-      <c r="L87" s="11" t="s">
+      <c r="L87" s="23" t="s">
         <v>2905</v>
       </c>
       <c r="M87" s="11"/>
@@ -15731,16 +15751,16 @@
       <c r="H88" s="11" t="s">
         <v>2909</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="23" t="s">
         <v>2910</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="23" t="s">
         <v>2911</v>
       </c>
-      <c r="L88" s="13" t="s">
+      <c r="L88" s="25" t="s">
         <v>2912</v>
       </c>
       <c r="M88" s="11"/>
@@ -15778,14 +15798,14 @@
       <c r="H89" s="11" t="s">
         <v>2917</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="23" t="s">
         <v>2918</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J89" s="23" t="s">
         <v>2919</v>
       </c>
-      <c r="K89" s="11"/>
-      <c r="L89" s="13" t="s">
+      <c r="K89" s="23"/>
+      <c r="L89" s="25" t="s">
         <v>2920</v>
       </c>
       <c r="M89" s="11"/>
@@ -15795,11 +15815,11 @@
       <c r="O89" s="11" t="s">
         <v>2921</v>
       </c>
-      <c r="P89" s="13" t="s">
+      <c r="P89" s="12" t="s">
         <v>2922</v>
       </c>
-      <c r="Q89" s="14"/>
-      <c r="R89" s="14"/>
+      <c r="Q89" s="13"/>
+      <c r="R89" s="13"/>
       <c r="S89" s="11" t="s">
         <v>2923</v>
       </c>
@@ -15829,14 +15849,14 @@
       <c r="H90" s="11" t="s">
         <v>2928</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J90" s="11"/>
-      <c r="K90" s="11" t="s">
+      <c r="J90" s="23"/>
+      <c r="K90" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L90" s="13" t="s">
+      <c r="L90" s="25" t="s">
         <v>2931</v>
       </c>
       <c r="M90" s="11"/>
@@ -15872,14 +15892,14 @@
       <c r="H91" s="11" t="s">
         <v>2936</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J91" s="11"/>
-      <c r="K91" s="11" t="s">
+      <c r="J91" s="23"/>
+      <c r="K91" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L91" s="11" t="s">
+      <c r="L91" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M91" s="11"/>
@@ -15889,12 +15909,12 @@
       <c r="O91" s="11" t="s">
         <v>2938</v>
       </c>
-      <c r="P91" s="13" t="s">
+      <c r="P91" s="12" t="s">
         <v>2939</v>
       </c>
-      <c r="Q91" s="14"/>
-      <c r="R91" s="14"/>
-      <c r="S91" s="14"/>
+      <c r="Q91" s="13"/>
+      <c r="R91" s="13"/>
+      <c r="S91" s="13"/>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="11" t="s">
@@ -15919,14 +15939,14 @@
       <c r="H92" s="11" t="s">
         <v>2942</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J92" s="11"/>
-      <c r="K92" s="11" t="s">
+      <c r="J92" s="23"/>
+      <c r="K92" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L92" s="11" t="s">
+      <c r="L92" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M92" s="11"/>
@@ -15962,14 +15982,14 @@
       <c r="H93" s="11" t="s">
         <v>2946</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J93" s="11"/>
-      <c r="K93" s="11" t="s">
+      <c r="J93" s="23"/>
+      <c r="K93" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L93" s="11" t="s">
+      <c r="L93" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M93" s="11"/>
@@ -16005,14 +16025,14 @@
       <c r="H94" s="11" t="s">
         <v>2949</v>
       </c>
-      <c r="I94" s="11" t="s">
+      <c r="I94" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J94" s="11"/>
-      <c r="K94" s="11" t="s">
+      <c r="J94" s="23"/>
+      <c r="K94" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L94" s="11" t="s">
+      <c r="L94" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M94" s="11"/>
@@ -16048,14 +16068,14 @@
       <c r="H95" s="11" t="s">
         <v>2954</v>
       </c>
-      <c r="I95" s="11" t="s">
+      <c r="I95" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J95" s="11"/>
-      <c r="K95" s="11" t="s">
+      <c r="J95" s="23"/>
+      <c r="K95" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L95" s="11" t="s">
+      <c r="L95" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M95" s="11"/>
@@ -16091,14 +16111,14 @@
       <c r="H96" s="11" t="s">
         <v>2958</v>
       </c>
-      <c r="I96" s="11" t="s">
+      <c r="I96" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J96" s="11"/>
-      <c r="K96" s="11" t="s">
+      <c r="J96" s="23"/>
+      <c r="K96" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L96" s="13" t="s">
+      <c r="L96" s="25" t="s">
         <v>2937</v>
       </c>
       <c r="M96" s="11"/>
@@ -16134,14 +16154,14 @@
       <c r="H97" s="11" t="s">
         <v>2962</v>
       </c>
-      <c r="I97" s="11" t="s">
+      <c r="I97" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J97" s="11"/>
-      <c r="K97" s="11" t="s">
+      <c r="J97" s="23"/>
+      <c r="K97" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L97" s="11" t="s">
+      <c r="L97" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M97" s="11"/>
@@ -16177,14 +16197,14 @@
       <c r="H98" s="11" t="s">
         <v>2966</v>
       </c>
-      <c r="I98" s="11" t="s">
+      <c r="I98" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J98" s="11"/>
-      <c r="K98" s="11" t="s">
+      <c r="J98" s="23"/>
+      <c r="K98" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L98" s="11" t="s">
+      <c r="L98" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M98" s="11"/>
@@ -16222,14 +16242,14 @@
       <c r="H99" s="11" t="s">
         <v>2972</v>
       </c>
-      <c r="I99" s="11" t="s">
+      <c r="I99" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J99" s="11"/>
-      <c r="K99" s="11" t="s">
+      <c r="J99" s="23"/>
+      <c r="K99" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L99" s="11" t="s">
+      <c r="L99" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M99" s="11"/>
@@ -16267,14 +16287,14 @@
       <c r="H100" s="11" t="s">
         <v>2977</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="I100" s="23" t="s">
         <v>2929</v>
       </c>
-      <c r="J100" s="11"/>
-      <c r="K100" s="11" t="s">
+      <c r="J100" s="23"/>
+      <c r="K100" s="23" t="s">
         <v>2930</v>
       </c>
-      <c r="L100" s="11" t="s">
+      <c r="L100" s="23" t="s">
         <v>2937</v>
       </c>
       <c r="M100" s="11"/>
@@ -16310,14 +16330,14 @@
       <c r="H101" s="11" t="s">
         <v>2983</v>
       </c>
-      <c r="I101" s="11" t="s">
+      <c r="I101" s="23" t="s">
         <v>2984</v>
       </c>
-      <c r="J101" s="11"/>
-      <c r="K101" s="11" t="s">
+      <c r="J101" s="23"/>
+      <c r="K101" s="23" t="s">
         <v>2985</v>
       </c>
-      <c r="L101" s="13" t="s">
+      <c r="L101" s="25" t="s">
         <v>2986</v>
       </c>
       <c r="M101" s="11"/>
@@ -16353,14 +16373,14 @@
       <c r="H102" s="11" t="s">
         <v>2991</v>
       </c>
-      <c r="I102" s="11" t="s">
+      <c r="I102" s="23" t="s">
         <v>2984</v>
       </c>
-      <c r="J102" s="11"/>
-      <c r="K102" s="11" t="s">
+      <c r="J102" s="23"/>
+      <c r="K102" s="23" t="s">
         <v>2985</v>
       </c>
-      <c r="L102" s="13" t="s">
+      <c r="L102" s="25" t="s">
         <v>2986</v>
       </c>
       <c r="M102" s="11"/>
@@ -16398,14 +16418,14 @@
       <c r="H103" s="11" t="s">
         <v>2996</v>
       </c>
-      <c r="I103" s="11" t="s">
+      <c r="I103" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J103" s="11"/>
-      <c r="K103" s="11" t="s">
+      <c r="J103" s="23"/>
+      <c r="K103" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L103" s="11" t="s">
+      <c r="L103" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M103" s="11" t="s">
@@ -16445,14 +16465,14 @@
       <c r="H104" s="11" t="s">
         <v>3005</v>
       </c>
-      <c r="I104" s="11" t="s">
+      <c r="I104" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J104" s="11"/>
-      <c r="K104" s="11" t="s">
+      <c r="J104" s="23"/>
+      <c r="K104" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L104" s="11" t="s">
+      <c r="L104" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M104" s="11" t="s">
@@ -16492,14 +16512,14 @@
       <c r="H105" s="11" t="s">
         <v>3011</v>
       </c>
-      <c r="I105" s="11" t="s">
+      <c r="I105" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J105" s="11"/>
-      <c r="K105" s="11" t="s">
+      <c r="J105" s="23"/>
+      <c r="K105" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L105" s="11" t="s">
+      <c r="L105" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M105" s="11"/>
@@ -16541,14 +16561,14 @@
       <c r="H106" s="11" t="s">
         <v>3018</v>
       </c>
-      <c r="I106" s="11" t="s">
+      <c r="I106" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J106" s="11"/>
-      <c r="K106" s="11" t="s">
+      <c r="J106" s="23"/>
+      <c r="K106" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L106" s="11" t="s">
+      <c r="L106" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M106" s="11" t="s">
@@ -16588,14 +16608,14 @@
       <c r="H107" s="11" t="s">
         <v>3022</v>
       </c>
-      <c r="I107" s="11" t="s">
+      <c r="I107" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J107" s="11"/>
-      <c r="K107" s="11" t="s">
+      <c r="J107" s="23"/>
+      <c r="K107" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L107" s="11" t="s">
+      <c r="L107" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M107" s="11"/>
@@ -16631,14 +16651,14 @@
       <c r="H108" s="11" t="s">
         <v>3027</v>
       </c>
-      <c r="I108" s="11" t="s">
+      <c r="I108" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J108" s="11"/>
-      <c r="K108" s="11" t="s">
+      <c r="J108" s="23"/>
+      <c r="K108" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L108" s="11" t="s">
+      <c r="L108" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M108" s="11" t="s">
@@ -16678,14 +16698,14 @@
       <c r="H109" s="11" t="s">
         <v>3031</v>
       </c>
-      <c r="I109" s="11" t="s">
+      <c r="I109" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J109" s="11"/>
-      <c r="K109" s="11" t="s">
+      <c r="J109" s="23"/>
+      <c r="K109" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L109" s="11" t="s">
+      <c r="L109" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M109" s="11" t="s">
@@ -16725,14 +16745,14 @@
       <c r="H110" s="11" t="s">
         <v>3034</v>
       </c>
-      <c r="I110" s="11" t="s">
+      <c r="I110" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J110" s="11"/>
-      <c r="K110" s="11" t="s">
+      <c r="J110" s="23"/>
+      <c r="K110" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L110" s="11" t="s">
+      <c r="L110" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M110" s="11" t="s">
@@ -16772,14 +16792,14 @@
       <c r="H111" s="11" t="s">
         <v>3037</v>
       </c>
-      <c r="I111" s="11" t="s">
+      <c r="I111" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J111" s="11"/>
-      <c r="K111" s="11" t="s">
+      <c r="J111" s="23"/>
+      <c r="K111" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L111" s="11" t="s">
+      <c r="L111" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M111" s="11" t="s">
@@ -16819,14 +16839,14 @@
       <c r="H112" s="11" t="s">
         <v>3042</v>
       </c>
-      <c r="I112" s="11" t="s">
+      <c r="I112" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J112" s="11"/>
-      <c r="K112" s="11" t="s">
+      <c r="J112" s="23"/>
+      <c r="K112" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L112" s="11" t="s">
+      <c r="L112" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M112" s="11" t="s">
@@ -16866,14 +16886,14 @@
       <c r="H113" s="11" t="s">
         <v>3045</v>
       </c>
-      <c r="I113" s="11" t="s">
+      <c r="I113" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J113" s="11"/>
-      <c r="K113" s="11" t="s">
+      <c r="J113" s="23"/>
+      <c r="K113" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L113" s="11" t="s">
+      <c r="L113" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M113" s="11" t="s">
@@ -16913,14 +16933,14 @@
       <c r="H114" s="11" t="s">
         <v>3050</v>
       </c>
-      <c r="I114" s="11" t="s">
+      <c r="I114" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J114" s="11"/>
-      <c r="K114" s="11" t="s">
+      <c r="J114" s="23"/>
+      <c r="K114" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L114" s="11" t="s">
+      <c r="L114" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M114" s="11" t="s">
@@ -16960,14 +16980,14 @@
       <c r="H115" s="11" t="s">
         <v>3053</v>
       </c>
-      <c r="I115" s="11" t="s">
+      <c r="I115" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J115" s="11"/>
-      <c r="K115" s="11" t="s">
+      <c r="J115" s="23"/>
+      <c r="K115" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L115" s="11" t="s">
+      <c r="L115" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M115" s="11" t="s">
@@ -17007,14 +17027,14 @@
       <c r="H116" s="11" t="s">
         <v>3058</v>
       </c>
-      <c r="I116" s="11" t="s">
+      <c r="I116" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J116" s="11"/>
-      <c r="K116" s="11" t="s">
+      <c r="J116" s="23"/>
+      <c r="K116" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L116" s="11" t="s">
+      <c r="L116" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M116" s="11" t="s">
@@ -17054,14 +17074,14 @@
       <c r="H117" s="11" t="s">
         <v>3062</v>
       </c>
-      <c r="I117" s="11" t="s">
+      <c r="I117" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J117" s="11"/>
-      <c r="K117" s="11" t="s">
+      <c r="J117" s="23"/>
+      <c r="K117" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L117" s="11" t="s">
+      <c r="L117" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M117" s="11" t="s">
@@ -17101,14 +17121,14 @@
       <c r="H118" s="11" t="s">
         <v>3067</v>
       </c>
-      <c r="I118" s="11" t="s">
+      <c r="I118" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J118" s="11"/>
-      <c r="K118" s="11" t="s">
+      <c r="J118" s="23"/>
+      <c r="K118" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L118" s="11" t="s">
+      <c r="L118" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M118" s="11"/>
@@ -17144,14 +17164,14 @@
       <c r="H119" s="11" t="s">
         <v>3071</v>
       </c>
-      <c r="I119" s="11" t="s">
+      <c r="I119" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J119" s="11"/>
-      <c r="K119" s="11" t="s">
+      <c r="J119" s="23"/>
+      <c r="K119" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L119" s="11" t="s">
+      <c r="L119" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M119" s="11" t="s">
@@ -17191,14 +17211,14 @@
       <c r="H120" s="11" t="s">
         <v>3074</v>
       </c>
-      <c r="I120" s="11" t="s">
+      <c r="I120" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J120" s="11"/>
-      <c r="K120" s="11" t="s">
+      <c r="J120" s="23"/>
+      <c r="K120" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L120" s="11" t="s">
+      <c r="L120" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M120" s="11" t="s">
@@ -17238,14 +17258,14 @@
       <c r="H121" s="11" t="s">
         <v>3079</v>
       </c>
-      <c r="I121" s="11" t="s">
+      <c r="I121" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J121" s="11"/>
-      <c r="K121" s="11" t="s">
+      <c r="J121" s="23"/>
+      <c r="K121" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L121" s="11" t="s">
+      <c r="L121" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M121" s="11" t="s">
@@ -17287,14 +17307,14 @@
       <c r="H122" s="11" t="s">
         <v>3083</v>
       </c>
-      <c r="I122" s="11" t="s">
+      <c r="I122" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J122" s="11"/>
-      <c r="K122" s="11" t="s">
+      <c r="J122" s="23"/>
+      <c r="K122" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L122" s="11" t="s">
+      <c r="L122" s="23" t="s">
         <v>2999</v>
       </c>
       <c r="M122" s="11" t="s">
@@ -17334,17 +17354,17 @@
       <c r="H123" s="11" t="s">
         <v>3088</v>
       </c>
-      <c r="I123" s="11" t="s">
+      <c r="I123" s="23" t="s">
         <v>2997</v>
       </c>
-      <c r="J123" s="11"/>
-      <c r="K123" s="11" t="s">
+      <c r="J123" s="23"/>
+      <c r="K123" s="23" t="s">
         <v>2998</v>
       </c>
-      <c r="L123" s="11" t="s">
+      <c r="L123" s="23" t="s">
         <v>2999</v>
       </c>
-      <c r="M123" s="16" t="s">
+      <c r="M123" s="15" t="s">
         <v>2383</v>
       </c>
       <c r="N123" s="11" t="s">
@@ -17381,18 +17401,18 @@
       <c r="H124" s="11" t="s">
         <v>3092</v>
       </c>
-      <c r="I124" s="16" t="s">
+      <c r="I124" s="27" t="s">
         <v>2997</v>
       </c>
-      <c r="J124" s="16"/>
-      <c r="K124" s="16" t="s">
+      <c r="J124" s="27"/>
+      <c r="K124" s="27" t="s">
         <v>2998</v>
       </c>
-      <c r="L124" s="17" t="s">
+      <c r="L124" s="28" t="s">
         <v>2999</v>
       </c>
       <c r="M124" s="11"/>
-      <c r="N124" s="18" t="s">
+      <c r="N124" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O124" s="11"/>
@@ -17421,23 +17441,23 @@
         <v>2250</v>
       </c>
       <c r="G125" s="11"/>
-      <c r="H125" s="19" t="s">
+      <c r="H125" s="17" t="s">
         <v>3097</v>
       </c>
-      <c r="I125" s="11" t="s">
+      <c r="I125" s="23" t="s">
         <v>3098</v>
       </c>
-      <c r="J125" s="11" t="s">
+      <c r="J125" s="23" t="s">
         <v>3099</v>
       </c>
-      <c r="K125" s="11" t="s">
+      <c r="K125" s="23" t="s">
         <v>3100</v>
       </c>
-      <c r="L125" s="20" t="s">
+      <c r="L125" s="29" t="s">
         <v>3101</v>
       </c>
       <c r="M125" s="11"/>
-      <c r="N125" s="18" t="s">
+      <c r="N125" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O125" s="11"/>
@@ -17468,23 +17488,23 @@
         <v>2250</v>
       </c>
       <c r="G126" s="11"/>
-      <c r="H126" s="19" t="s">
+      <c r="H126" s="17" t="s">
         <v>3105</v>
       </c>
-      <c r="I126" s="11" t="s">
+      <c r="I126" s="23" t="s">
         <v>3098</v>
       </c>
-      <c r="J126" s="11" t="s">
+      <c r="J126" s="23" t="s">
         <v>3099</v>
       </c>
-      <c r="K126" s="11" t="s">
+      <c r="K126" s="23" t="s">
         <v>3100</v>
       </c>
-      <c r="L126" s="20" t="s">
+      <c r="L126" s="29" t="s">
         <v>3101</v>
       </c>
       <c r="M126" s="11"/>
-      <c r="N126" s="18" t="s">
+      <c r="N126" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O126" s="11"/>
@@ -17515,23 +17535,23 @@
         <v>2250</v>
       </c>
       <c r="G127" s="11"/>
-      <c r="H127" s="19" t="s">
+      <c r="H127" s="17" t="s">
         <v>3110</v>
       </c>
-      <c r="I127" s="11" t="s">
+      <c r="I127" s="23" t="s">
         <v>3098</v>
       </c>
-      <c r="J127" s="11" t="s">
+      <c r="J127" s="23" t="s">
         <v>3099</v>
       </c>
-      <c r="K127" s="11" t="s">
+      <c r="K127" s="23" t="s">
         <v>3100</v>
       </c>
-      <c r="L127" s="20" t="s">
+      <c r="L127" s="29" t="s">
         <v>3101</v>
       </c>
       <c r="M127" s="11"/>
-      <c r="N127" s="18" t="s">
+      <c r="N127" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O127" s="11"/>
@@ -17562,23 +17582,23 @@
         <v>2250</v>
       </c>
       <c r="G128" s="11"/>
-      <c r="H128" s="19" t="s">
+      <c r="H128" s="17" t="s">
         <v>3113</v>
       </c>
-      <c r="I128" s="11" t="s">
+      <c r="I128" s="23" t="s">
         <v>3098</v>
       </c>
-      <c r="J128" s="11" t="s">
+      <c r="J128" s="23" t="s">
         <v>3099</v>
       </c>
-      <c r="K128" s="11" t="s">
+      <c r="K128" s="23" t="s">
         <v>3100</v>
       </c>
-      <c r="L128" s="20" t="s">
+      <c r="L128" s="29" t="s">
         <v>3101</v>
       </c>
       <c r="M128" s="11"/>
-      <c r="N128" s="18" t="s">
+      <c r="N128" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O128" s="11"/>
@@ -17607,21 +17627,21 @@
         <v>2250</v>
       </c>
       <c r="G129" s="11"/>
-      <c r="H129" s="19"/>
-      <c r="I129" s="21" t="s">
+      <c r="H129" s="17"/>
+      <c r="I129" s="30" t="s">
         <v>3098</v>
       </c>
-      <c r="J129" s="21" t="s">
+      <c r="J129" s="30" t="s">
         <v>3099</v>
       </c>
-      <c r="K129" s="21" t="s">
+      <c r="K129" s="30" t="s">
         <v>3100</v>
       </c>
-      <c r="L129" s="22" t="s">
+      <c r="L129" s="31" t="s">
         <v>3101</v>
       </c>
       <c r="M129" s="11"/>
-      <c r="N129" s="18" t="s">
+      <c r="N129" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O129" s="11"/>
@@ -17650,21 +17670,21 @@
         <v>2250</v>
       </c>
       <c r="G130" s="11"/>
-      <c r="H130" s="19"/>
-      <c r="I130" s="21" t="s">
+      <c r="H130" s="17"/>
+      <c r="I130" s="30" t="s">
         <v>3098</v>
       </c>
-      <c r="J130" s="21" t="s">
+      <c r="J130" s="30" t="s">
         <v>3099</v>
       </c>
-      <c r="K130" s="21" t="s">
+      <c r="K130" s="30" t="s">
         <v>3100</v>
       </c>
-      <c r="L130" s="22" t="s">
+      <c r="L130" s="31" t="s">
         <v>3101</v>
       </c>
       <c r="M130" s="11"/>
-      <c r="N130" s="18" t="s">
+      <c r="N130" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O130" s="11"/>
@@ -17695,23 +17715,23 @@
         <v>2250</v>
       </c>
       <c r="G131" s="11"/>
-      <c r="H131" s="19" t="s">
+      <c r="H131" s="17" t="s">
         <v>3121</v>
       </c>
-      <c r="I131" s="11" t="s">
+      <c r="I131" s="23" t="s">
         <v>3098</v>
       </c>
-      <c r="J131" s="11" t="s">
+      <c r="J131" s="23" t="s">
         <v>3099</v>
       </c>
-      <c r="K131" s="23" t="s">
+      <c r="K131" s="32" t="s">
         <v>3100</v>
       </c>
-      <c r="L131" s="24" t="s">
+      <c r="L131" s="33" t="s">
         <v>3101</v>
       </c>
       <c r="M131" s="11"/>
-      <c r="N131" s="18" t="s">
+      <c r="N131" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O131" s="11"/>
@@ -17747,30 +17767,30 @@
       <c r="H132" s="11" t="s">
         <v>3127</v>
       </c>
-      <c r="I132" s="25" t="s">
+      <c r="I132" s="34" t="s">
         <v>3128</v>
       </c>
-      <c r="J132" s="25" t="s">
+      <c r="J132" s="34" t="s">
         <v>2762</v>
       </c>
-      <c r="K132" s="26" t="s">
+      <c r="K132" s="35" t="s">
         <v>3129</v>
       </c>
-      <c r="L132" s="27" t="s">
+      <c r="L132" s="36" t="s">
         <v>3130</v>
       </c>
-      <c r="M132" s="28"/>
-      <c r="N132" s="18" t="s">
+      <c r="M132" s="18"/>
+      <c r="N132" s="16" t="s">
         <v>2255</v>
       </c>
       <c r="O132" s="11" t="s">
         <v>3131</v>
       </c>
-      <c r="P132" s="13" t="s">
+      <c r="P132" s="12" t="s">
         <v>3132</v>
       </c>
-      <c r="Q132" s="14"/>
-      <c r="R132" s="14"/>
+      <c r="Q132" s="13"/>
+      <c r="R132" s="13"/>
       <c r="S132" s="11" t="s">
         <v>3133</v>
       </c>
@@ -17798,30 +17818,30 @@
       <c r="H133" s="11" t="s">
         <v>3136</v>
       </c>
-      <c r="I133" s="29" t="s">
+      <c r="I133" s="30" t="s">
         <v>3137</v>
       </c>
-      <c r="J133" s="29" t="s">
+      <c r="J133" s="30" t="s">
         <v>2762</v>
       </c>
-      <c r="K133" s="30" t="s">
+      <c r="K133" s="37" t="s">
         <v>3138</v>
       </c>
-      <c r="L133" s="31" t="s">
+      <c r="L133" s="38" t="s">
         <v>3139</v>
       </c>
-      <c r="M133" s="32"/>
+      <c r="M133" s="19"/>
       <c r="N133" s="11" t="s">
         <v>2255</v>
       </c>
       <c r="O133" s="11" t="s">
         <v>3131</v>
       </c>
-      <c r="P133" s="13" t="s">
+      <c r="P133" s="12" t="s">
         <v>3132</v>
       </c>
-      <c r="Q133" s="14"/>
-      <c r="R133" s="14"/>
+      <c r="Q133" s="13"/>
+      <c r="R133" s="13"/>
       <c r="S133" s="11" t="s">
         <v>3140</v>
       </c>
@@ -17849,30 +17869,30 @@
       <c r="H134" s="11" t="s">
         <v>3143</v>
       </c>
-      <c r="I134" s="29" t="s">
+      <c r="I134" s="30" t="s">
         <v>3144</v>
       </c>
-      <c r="J134" s="29" t="s">
+      <c r="J134" s="30" t="s">
         <v>2762</v>
       </c>
-      <c r="K134" s="30" t="s">
+      <c r="K134" s="37" t="s">
         <v>3145</v>
       </c>
-      <c r="L134" s="31" t="s">
+      <c r="L134" s="38" t="s">
         <v>3146</v>
       </c>
-      <c r="M134" s="28"/>
+      <c r="M134" s="18"/>
       <c r="N134" s="11" t="s">
         <v>2255</v>
       </c>
       <c r="O134" s="11" t="s">
         <v>3131</v>
       </c>
-      <c r="P134" s="13" t="s">
+      <c r="P134" s="12" t="s">
         <v>3132</v>
       </c>
-      <c r="Q134" s="14"/>
-      <c r="R134" s="14"/>
+      <c r="Q134" s="13"/>
+      <c r="R134" s="13"/>
       <c r="S134" s="11" t="s">
         <v>3140</v>
       </c>
@@ -17900,30 +17920,30 @@
       <c r="H135" s="11" t="s">
         <v>3149</v>
       </c>
-      <c r="I135" s="29" t="s">
+      <c r="I135" s="30" t="s">
         <v>3150</v>
       </c>
-      <c r="J135" s="29" t="s">
+      <c r="J135" s="30" t="s">
         <v>2762</v>
       </c>
-      <c r="K135" s="30" t="s">
+      <c r="K135" s="37" t="s">
         <v>3151</v>
       </c>
-      <c r="L135" s="31" t="s">
+      <c r="L135" s="38" t="s">
         <v>3152</v>
       </c>
-      <c r="M135" s="28"/>
+      <c r="M135" s="18"/>
       <c r="N135" s="11" t="s">
         <v>2255</v>
       </c>
       <c r="O135" s="11" t="s">
         <v>3131</v>
       </c>
-      <c r="P135" s="13" t="s">
+      <c r="P135" s="12" t="s">
         <v>3132</v>
       </c>
-      <c r="Q135" s="14"/>
-      <c r="R135" s="14"/>
+      <c r="Q135" s="13"/>
+      <c r="R135" s="13"/>
       <c r="S135" s="11" t="s">
         <v>3140</v>
       </c>
@@ -17947,16 +17967,16 @@
       </c>
       <c r="G136" s="11"/>
       <c r="H136" s="11"/>
-      <c r="I136" s="11" t="s">
+      <c r="I136" s="23" t="s">
         <v>3157</v>
       </c>
-      <c r="J136" s="11" t="s">
+      <c r="J136" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K136" s="23" t="s">
+      <c r="K136" s="32" t="s">
         <v>3158</v>
       </c>
-      <c r="L136" s="33" t="s">
+      <c r="L136" s="39" t="s">
         <v>3159</v>
       </c>
       <c r="M136" s="11"/>
@@ -17994,16 +18014,16 @@
       <c r="H137" s="11" t="s">
         <v>3163</v>
       </c>
-      <c r="I137" s="21" t="s">
+      <c r="I137" s="30" t="s">
         <v>3157</v>
       </c>
-      <c r="J137" s="21" t="s">
+      <c r="J137" s="30" t="s">
         <v>2304</v>
       </c>
-      <c r="K137" s="21" t="s">
+      <c r="K137" s="30" t="s">
         <v>3158</v>
       </c>
-      <c r="L137" s="34" t="s">
+      <c r="L137" s="40" t="s">
         <v>3159</v>
       </c>
       <c r="M137" s="11"/>
@@ -18041,16 +18061,16 @@
       <c r="H138" s="11" t="s">
         <v>3166</v>
       </c>
-      <c r="I138" s="11" t="s">
+      <c r="I138" s="23" t="s">
         <v>3157</v>
       </c>
-      <c r="J138" s="11" t="s">
+      <c r="J138" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K138" s="11" t="s">
+      <c r="K138" s="23" t="s">
         <v>3158</v>
       </c>
-      <c r="L138" s="13" t="s">
+      <c r="L138" s="25" t="s">
         <v>3159</v>
       </c>
       <c r="M138" s="11"/>
@@ -18088,16 +18108,16 @@
       <c r="H139" s="11" t="s">
         <v>3172</v>
       </c>
-      <c r="I139" s="11" t="s">
+      <c r="I139" s="23" t="s">
         <v>3173</v>
       </c>
-      <c r="J139" s="11" t="s">
+      <c r="J139" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K139" s="11" t="s">
+      <c r="K139" s="23" t="s">
         <v>3172</v>
       </c>
-      <c r="L139" s="13" t="s">
+      <c r="L139" s="25" t="s">
         <v>3174</v>
       </c>
       <c r="M139" s="11"/>
@@ -18107,11 +18127,11 @@
       <c r="O139" s="11" t="s">
         <v>3175</v>
       </c>
-      <c r="P139" s="13" t="s">
+      <c r="P139" s="12" t="s">
         <v>3176</v>
       </c>
-      <c r="Q139" s="14"/>
-      <c r="R139" s="14"/>
+      <c r="Q139" s="13"/>
+      <c r="R139" s="13"/>
       <c r="S139" s="11" t="s">
         <v>3177</v>
       </c>
@@ -18139,14 +18159,14 @@
       <c r="H140" s="11" t="s">
         <v>3182</v>
       </c>
-      <c r="I140" s="11" t="s">
+      <c r="I140" s="23" t="s">
         <v>3183</v>
       </c>
-      <c r="J140" s="11"/>
-      <c r="K140" s="11" t="s">
+      <c r="J140" s="23"/>
+      <c r="K140" s="23" t="s">
         <v>3184</v>
       </c>
-      <c r="L140" s="13" t="s">
+      <c r="L140" s="25" t="s">
         <v>3185</v>
       </c>
       <c r="M140" s="11"/>
@@ -18184,14 +18204,14 @@
       <c r="H141" s="11" t="s">
         <v>3192</v>
       </c>
-      <c r="I141" s="11" t="s">
+      <c r="I141" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J141" s="11"/>
-      <c r="K141" s="11" t="s">
+      <c r="J141" s="23"/>
+      <c r="K141" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L141" s="11" t="s">
+      <c r="L141" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M141" s="11" t="s">
@@ -18231,14 +18251,14 @@
       <c r="H142" s="11" t="s">
         <v>3201</v>
       </c>
-      <c r="I142" s="11" t="s">
+      <c r="I142" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J142" s="11"/>
-      <c r="K142" s="11" t="s">
+      <c r="J142" s="23"/>
+      <c r="K142" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L142" s="11" t="s">
+      <c r="L142" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M142" s="11" t="s">
@@ -18278,14 +18298,14 @@
       <c r="H143" s="11" t="s">
         <v>3205</v>
       </c>
-      <c r="I143" s="11" t="s">
+      <c r="I143" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J143" s="11"/>
-      <c r="K143" s="11" t="s">
+      <c r="J143" s="23"/>
+      <c r="K143" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L143" s="11" t="s">
+      <c r="L143" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M143" s="11" t="s">
@@ -18323,14 +18343,14 @@
       <c r="H144" s="11" t="s">
         <v>3210</v>
       </c>
-      <c r="I144" s="11" t="s">
+      <c r="I144" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J144" s="11"/>
-      <c r="K144" s="11" t="s">
+      <c r="J144" s="23"/>
+      <c r="K144" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L144" s="11" t="s">
+      <c r="L144" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M144" s="11"/>
@@ -18368,14 +18388,14 @@
       <c r="H145" s="11" t="s">
         <v>3214</v>
       </c>
-      <c r="I145" s="11" t="s">
+      <c r="I145" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J145" s="11"/>
-      <c r="K145" s="11" t="s">
+      <c r="J145" s="23"/>
+      <c r="K145" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L145" s="11" t="s">
+      <c r="L145" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M145" s="11" t="s">
@@ -18409,14 +18429,14 @@
       </c>
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
-      <c r="I146" s="11" t="s">
+      <c r="I146" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J146" s="11"/>
-      <c r="K146" s="11" t="s">
+      <c r="J146" s="23"/>
+      <c r="K146" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L146" s="11" t="s">
+      <c r="L146" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M146" s="11"/>
@@ -18450,14 +18470,14 @@
       </c>
       <c r="G147" s="11"/>
       <c r="H147" s="11"/>
-      <c r="I147" s="11" t="s">
+      <c r="I147" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J147" s="11"/>
-      <c r="K147" s="11" t="s">
+      <c r="J147" s="23"/>
+      <c r="K147" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L147" s="11" t="s">
+      <c r="L147" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M147" s="11"/>
@@ -18495,14 +18515,14 @@
       <c r="H148" s="11" t="s">
         <v>3224</v>
       </c>
-      <c r="I148" s="11" t="s">
+      <c r="I148" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J148" s="11"/>
-      <c r="K148" s="11" t="s">
+      <c r="J148" s="23"/>
+      <c r="K148" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L148" s="11" t="s">
+      <c r="L148" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M148" s="11" t="s">
@@ -18540,14 +18560,14 @@
       <c r="H149" s="11" t="s">
         <v>3228</v>
       </c>
-      <c r="I149" s="11" t="s">
+      <c r="I149" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J149" s="11"/>
-      <c r="K149" s="11" t="s">
+      <c r="J149" s="23"/>
+      <c r="K149" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L149" s="11" t="s">
+      <c r="L149" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M149" s="11" t="s">
@@ -18585,14 +18605,14 @@
       <c r="H150" s="11" t="s">
         <v>3232</v>
       </c>
-      <c r="I150" s="11" t="s">
+      <c r="I150" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J150" s="11"/>
-      <c r="K150" s="11" t="s">
+      <c r="J150" s="23"/>
+      <c r="K150" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L150" s="11" t="s">
+      <c r="L150" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M150" s="11" t="s">
@@ -18632,14 +18652,14 @@
       <c r="H151" s="11" t="s">
         <v>3238</v>
       </c>
-      <c r="I151" s="11" t="s">
+      <c r="I151" s="23" t="s">
         <v>3193</v>
       </c>
-      <c r="J151" s="11"/>
-      <c r="K151" s="11" t="s">
+      <c r="J151" s="23"/>
+      <c r="K151" s="23" t="s">
         <v>3194</v>
       </c>
-      <c r="L151" s="11" t="s">
+      <c r="L151" s="23" t="s">
         <v>3195</v>
       </c>
       <c r="M151" s="11"/>
@@ -18649,11 +18669,11 @@
       <c r="O151" s="11" t="s">
         <v>3239</v>
       </c>
-      <c r="P151" s="13" t="s">
+      <c r="P151" s="12" t="s">
         <v>3240</v>
       </c>
-      <c r="Q151" s="14"/>
-      <c r="R151" s="14"/>
+      <c r="Q151" s="13"/>
+      <c r="R151" s="13"/>
       <c r="S151" s="11" t="s">
         <v>3241</v>
       </c>
@@ -18681,14 +18701,14 @@
       <c r="H152" s="11" t="s">
         <v>3246</v>
       </c>
-      <c r="I152" s="11" t="s">
+      <c r="I152" s="23" t="s">
         <v>3247</v>
       </c>
-      <c r="J152" s="11"/>
-      <c r="K152" s="11" t="s">
+      <c r="J152" s="23"/>
+      <c r="K152" s="23" t="s">
         <v>3248</v>
       </c>
-      <c r="L152" s="13" t="s">
+      <c r="L152" s="25" t="s">
         <v>3249</v>
       </c>
       <c r="M152" s="11"/>
@@ -18724,14 +18744,14 @@
       <c r="H153" s="11" t="s">
         <v>3248</v>
       </c>
-      <c r="I153" s="11" t="s">
+      <c r="I153" s="23" t="s">
         <v>3247</v>
       </c>
-      <c r="J153" s="11"/>
-      <c r="K153" s="11" t="s">
+      <c r="J153" s="23"/>
+      <c r="K153" s="23" t="s">
         <v>3248</v>
       </c>
-      <c r="L153" s="11" t="s">
+      <c r="L153" s="23" t="s">
         <v>3249</v>
       </c>
       <c r="M153" s="11"/>
@@ -18767,14 +18787,14 @@
       <c r="H154" s="11" t="s">
         <v>3257</v>
       </c>
-      <c r="I154" s="11" t="s">
+      <c r="I154" s="23" t="s">
         <v>3258</v>
       </c>
-      <c r="J154" s="11"/>
-      <c r="K154" s="11" t="s">
+      <c r="J154" s="23"/>
+      <c r="K154" s="23" t="s">
         <v>3259</v>
       </c>
-      <c r="L154" s="11" t="s">
+      <c r="L154" s="23" t="s">
         <v>3260</v>
       </c>
       <c r="M154" s="11" t="s">
@@ -18814,14 +18834,14 @@
       <c r="H155" s="11" t="s">
         <v>3264</v>
       </c>
-      <c r="I155" s="11" t="s">
+      <c r="I155" s="23" t="s">
         <v>3258</v>
       </c>
-      <c r="J155" s="11"/>
-      <c r="K155" s="11" t="s">
+      <c r="J155" s="23"/>
+      <c r="K155" s="23" t="s">
         <v>3259</v>
       </c>
-      <c r="L155" s="11" t="s">
+      <c r="L155" s="23" t="s">
         <v>3260</v>
       </c>
       <c r="M155" s="11" t="s">
@@ -18859,14 +18879,14 @@
       <c r="H156" s="11" t="s">
         <v>3268</v>
       </c>
-      <c r="I156" s="11" t="s">
+      <c r="I156" s="23" t="s">
         <v>3258</v>
       </c>
-      <c r="J156" s="11"/>
-      <c r="K156" s="11" t="s">
+      <c r="J156" s="23"/>
+      <c r="K156" s="23" t="s">
         <v>3259</v>
       </c>
-      <c r="L156" s="11" t="s">
+      <c r="L156" s="23" t="s">
         <v>3260</v>
       </c>
       <c r="M156" s="11" t="s">
@@ -18906,14 +18926,14 @@
       <c r="H157" s="11" t="s">
         <v>3273</v>
       </c>
-      <c r="I157" s="11" t="s">
+      <c r="I157" s="23" t="s">
         <v>3258</v>
       </c>
-      <c r="J157" s="11"/>
-      <c r="K157" s="11" t="s">
+      <c r="J157" s="23"/>
+      <c r="K157" s="23" t="s">
         <v>3259</v>
       </c>
-      <c r="L157" s="11" t="s">
+      <c r="L157" s="23" t="s">
         <v>3260</v>
       </c>
       <c r="M157" s="11" t="s">
@@ -18951,14 +18971,14 @@
       <c r="H158" s="11" t="s">
         <v>3278</v>
       </c>
-      <c r="I158" s="11" t="s">
+      <c r="I158" s="23" t="s">
         <v>3279</v>
       </c>
-      <c r="J158" s="11"/>
-      <c r="K158" s="11" t="s">
+      <c r="J158" s="23"/>
+      <c r="K158" s="23" t="s">
         <v>3278</v>
       </c>
-      <c r="L158" s="13" t="s">
+      <c r="L158" s="25" t="s">
         <v>3280</v>
       </c>
       <c r="M158" s="11"/>
@@ -18996,14 +19016,14 @@
       <c r="H159" s="11" t="s">
         <v>3285</v>
       </c>
-      <c r="I159" s="11" t="s">
+      <c r="I159" s="23" t="s">
         <v>3286</v>
       </c>
-      <c r="J159" s="11"/>
-      <c r="K159" s="11" t="s">
+      <c r="J159" s="23"/>
+      <c r="K159" s="23" t="s">
         <v>3285</v>
       </c>
-      <c r="L159" s="13" t="s">
+      <c r="L159" s="25" t="s">
         <v>3287</v>
       </c>
       <c r="M159" s="11"/>
@@ -19041,14 +19061,14 @@
       <c r="H160" s="11" t="s">
         <v>3294</v>
       </c>
-      <c r="I160" s="11" t="s">
+      <c r="I160" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J160" s="11"/>
-      <c r="K160" s="35" t="s">
+      <c r="J160" s="23"/>
+      <c r="K160" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L160" s="11" t="s">
+      <c r="L160" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M160" s="11" t="s">
@@ -19060,7 +19080,7 @@
       <c r="O160" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P160" s="13" t="s">
+      <c r="P160" s="12" t="s">
         <v>3299</v>
       </c>
       <c r="Q160" s="11" t="s">
@@ -19094,14 +19114,14 @@
       <c r="H161" s="11" t="s">
         <v>3305</v>
       </c>
-      <c r="I161" s="11" t="s">
+      <c r="I161" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J161" s="11"/>
-      <c r="K161" s="35" t="s">
+      <c r="J161" s="23"/>
+      <c r="K161" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L161" s="11" t="s">
+      <c r="L161" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M161" s="11" t="s">
@@ -19113,7 +19133,7 @@
       <c r="O161" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P161" s="13" t="s">
+      <c r="P161" s="12" t="s">
         <v>3299</v>
       </c>
       <c r="Q161" s="11" t="s">
@@ -19143,14 +19163,14 @@
       </c>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
-      <c r="I162" s="11" t="s">
+      <c r="I162" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J162" s="11"/>
-      <c r="K162" s="35" t="s">
+      <c r="J162" s="23"/>
+      <c r="K162" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L162" s="11" t="s">
+      <c r="L162" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M162" s="11" t="s">
@@ -19194,14 +19214,14 @@
       <c r="H163" s="11" t="s">
         <v>3317</v>
       </c>
-      <c r="I163" s="11" t="s">
+      <c r="I163" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J163" s="11"/>
-      <c r="K163" s="35" t="s">
+      <c r="J163" s="23"/>
+      <c r="K163" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L163" s="11" t="s">
+      <c r="L163" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M163" s="11" t="s">
@@ -19213,11 +19233,11 @@
       <c r="O163" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P163" s="13" t="s">
+      <c r="P163" s="12" t="s">
         <v>3299</v>
       </c>
-      <c r="Q163" s="14"/>
-      <c r="R163" s="14"/>
+      <c r="Q163" s="13"/>
+      <c r="R163" s="13"/>
       <c r="S163" s="11" t="s">
         <v>3307</v>
       </c>
@@ -19245,14 +19265,14 @@
       <c r="H164" s="11" t="s">
         <v>3320</v>
       </c>
-      <c r="I164" s="11" t="s">
+      <c r="I164" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J164" s="11"/>
-      <c r="K164" s="35" t="s">
+      <c r="J164" s="23"/>
+      <c r="K164" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L164" s="11" t="s">
+      <c r="L164" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M164" s="11" t="s">
@@ -19264,7 +19284,7 @@
       <c r="O164" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P164" s="13" t="s">
+      <c r="P164" s="12" t="s">
         <v>3299</v>
       </c>
       <c r="Q164" s="11" t="s">
@@ -19300,14 +19320,14 @@
       <c r="H165" s="11" t="s">
         <v>3323</v>
       </c>
-      <c r="I165" s="11" t="s">
+      <c r="I165" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J165" s="11"/>
-      <c r="K165" s="35" t="s">
+      <c r="J165" s="23"/>
+      <c r="K165" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L165" s="11" t="s">
+      <c r="L165" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M165" s="11" t="s">
@@ -19319,11 +19339,11 @@
       <c r="O165" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P165" s="13" t="s">
+      <c r="P165" s="12" t="s">
         <v>3299</v>
       </c>
-      <c r="Q165" s="14"/>
-      <c r="R165" s="14"/>
+      <c r="Q165" s="13"/>
+      <c r="R165" s="13"/>
       <c r="S165" s="11" t="s">
         <v>3324</v>
       </c>
@@ -19351,14 +19371,14 @@
       <c r="H166" s="11" t="s">
         <v>3328</v>
       </c>
-      <c r="I166" s="11" t="s">
+      <c r="I166" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J166" s="11"/>
-      <c r="K166" s="35" t="s">
+      <c r="J166" s="23"/>
+      <c r="K166" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L166" s="11" t="s">
+      <c r="L166" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M166" s="11" t="s">
@@ -19370,11 +19390,11 @@
       <c r="O166" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P166" s="13" t="s">
+      <c r="P166" s="12" t="s">
         <v>3299</v>
       </c>
-      <c r="Q166" s="14"/>
-      <c r="R166" s="14"/>
+      <c r="Q166" s="13"/>
+      <c r="R166" s="13"/>
       <c r="S166" s="11" t="s">
         <v>3307</v>
       </c>
@@ -19402,14 +19422,14 @@
       <c r="H167" s="11" t="s">
         <v>3333</v>
       </c>
-      <c r="I167" s="11" t="s">
+      <c r="I167" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J167" s="11"/>
-      <c r="K167" s="11" t="s">
+      <c r="J167" s="23"/>
+      <c r="K167" s="23" t="s">
         <v>3296</v>
       </c>
-      <c r="L167" s="11" t="s">
+      <c r="L167" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M167" s="11" t="s">
@@ -19421,11 +19441,11 @@
       <c r="O167" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P167" s="13" t="s">
+      <c r="P167" s="12" t="s">
         <v>3299</v>
       </c>
-      <c r="Q167" s="14"/>
-      <c r="R167" s="14"/>
+      <c r="Q167" s="13"/>
+      <c r="R167" s="13"/>
       <c r="S167" s="11" t="s">
         <v>3307</v>
       </c>
@@ -19453,14 +19473,14 @@
       <c r="H168" s="11" t="s">
         <v>3336</v>
       </c>
-      <c r="I168" s="11" t="s">
+      <c r="I168" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J168" s="11"/>
-      <c r="K168" s="35" t="s">
+      <c r="J168" s="23"/>
+      <c r="K168" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L168" s="11" t="s">
+      <c r="L168" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M168" s="11" t="s">
@@ -19472,7 +19492,7 @@
       <c r="O168" s="11" t="s">
         <v>3337</v>
       </c>
-      <c r="P168" s="13" t="s">
+      <c r="P168" s="12" t="s">
         <v>3338</v>
       </c>
       <c r="Q168" s="11" t="s">
@@ -19508,14 +19528,14 @@
       <c r="H169" s="11" t="s">
         <v>3344</v>
       </c>
-      <c r="I169" s="11" t="s">
+      <c r="I169" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J169" s="11"/>
-      <c r="K169" s="35" t="s">
+      <c r="J169" s="23"/>
+      <c r="K169" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L169" s="11" t="s">
+      <c r="L169" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M169" s="11" t="s">
@@ -19527,7 +19547,7 @@
       <c r="O169" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P169" s="13" t="s">
+      <c r="P169" s="12" t="s">
         <v>3299</v>
       </c>
       <c r="Q169" s="11" t="s">
@@ -19565,14 +19585,14 @@
       <c r="H170" s="11" t="s">
         <v>3352</v>
       </c>
-      <c r="I170" s="11" t="s">
+      <c r="I170" s="23" t="s">
         <v>3295</v>
       </c>
-      <c r="J170" s="11"/>
-      <c r="K170" s="35" t="s">
+      <c r="J170" s="23"/>
+      <c r="K170" s="41" t="s">
         <v>3296</v>
       </c>
-      <c r="L170" s="11" t="s">
+      <c r="L170" s="23" t="s">
         <v>3297</v>
       </c>
       <c r="M170" s="11" t="s">
@@ -19584,7 +19604,7 @@
       <c r="O170" s="11" t="s">
         <v>3298</v>
       </c>
-      <c r="P170" s="13" t="s">
+      <c r="P170" s="12" t="s">
         <v>3299</v>
       </c>
       <c r="Q170" s="11" t="s">
@@ -19622,14 +19642,14 @@
       <c r="H171" s="11" t="s">
         <v>3360</v>
       </c>
-      <c r="I171" s="11" t="s">
+      <c r="I171" s="23" t="s">
         <v>3361</v>
       </c>
-      <c r="J171" s="11"/>
-      <c r="K171" s="11" t="s">
+      <c r="J171" s="23"/>
+      <c r="K171" s="23" t="s">
         <v>3360</v>
       </c>
-      <c r="L171" s="13" t="s">
+      <c r="L171" s="25" t="s">
         <v>3362</v>
       </c>
       <c r="M171" s="11" t="s">
@@ -19669,14 +19689,14 @@
       <c r="H172" s="11" t="s">
         <v>3369</v>
       </c>
-      <c r="I172" s="11" t="s">
+      <c r="I172" s="23" t="s">
         <v>3370</v>
       </c>
-      <c r="J172" s="11" t="s">
+      <c r="J172" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K172" s="11"/>
-      <c r="L172" s="13" t="s">
+      <c r="K172" s="23"/>
+      <c r="L172" s="25" t="s">
         <v>3371</v>
       </c>
       <c r="M172" s="11" t="s">
@@ -19688,11 +19708,11 @@
       <c r="O172" s="11" t="s">
         <v>3372</v>
       </c>
-      <c r="P172" s="13" t="s">
+      <c r="P172" s="12" t="s">
         <v>3371</v>
       </c>
-      <c r="Q172" s="14"/>
-      <c r="R172" s="14"/>
+      <c r="Q172" s="13"/>
+      <c r="R172" s="13"/>
       <c r="S172" s="11" t="s">
         <v>3373</v>
       </c>
@@ -19716,14 +19736,14 @@
       </c>
       <c r="G173" s="11"/>
       <c r="H173" s="11"/>
-      <c r="I173" s="11" t="s">
+      <c r="I173" s="23" t="s">
         <v>3370</v>
       </c>
-      <c r="J173" s="11" t="s">
+      <c r="J173" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K173" s="11"/>
-      <c r="L173" s="13" t="s">
+      <c r="K173" s="23"/>
+      <c r="L173" s="25" t="s">
         <v>3371</v>
       </c>
       <c r="M173" s="11"/>
@@ -19761,14 +19781,14 @@
       </c>
       <c r="G174" s="11"/>
       <c r="H174" s="11"/>
-      <c r="I174" s="11" t="s">
+      <c r="I174" s="23" t="s">
         <v>3370</v>
       </c>
-      <c r="J174" s="11" t="s">
+      <c r="J174" s="23" t="s">
         <v>2304</v>
       </c>
-      <c r="K174" s="11"/>
-      <c r="L174" s="13" t="s">
+      <c r="K174" s="23"/>
+      <c r="L174" s="25" t="s">
         <v>3371</v>
       </c>
       <c r="M174" s="11"/>
@@ -19808,14 +19828,14 @@
       <c r="H175" s="11" t="s">
         <v>3383</v>
       </c>
-      <c r="I175" s="11" t="s">
+      <c r="I175" s="23" t="s">
         <v>3384</v>
       </c>
-      <c r="J175" s="11"/>
-      <c r="K175" s="11" t="s">
+      <c r="J175" s="23"/>
+      <c r="K175" s="23" t="s">
         <v>3385</v>
       </c>
-      <c r="L175" s="11" t="s">
+      <c r="L175" s="23" t="s">
         <v>3386</v>
       </c>
       <c r="M175" s="11"/>
@@ -19853,14 +19873,14 @@
       <c r="H176" s="11" t="s">
         <v>3390</v>
       </c>
-      <c r="I176" s="11" t="s">
+      <c r="I176" s="23" t="s">
         <v>3391</v>
       </c>
-      <c r="J176" s="11"/>
-      <c r="K176" s="11" t="s">
+      <c r="J176" s="23"/>
+      <c r="K176" s="23" t="s">
         <v>3392</v>
       </c>
-      <c r="L176" s="13" t="s">
+      <c r="L176" s="25" t="s">
         <v>3393</v>
       </c>
       <c r="M176" s="11"/>
@@ -19898,17 +19918,17 @@
       <c r="H177" s="11" t="s">
         <v>3399</v>
       </c>
-      <c r="I177" s="11" t="s">
+      <c r="I177" s="23" t="s">
         <v>3400</v>
       </c>
-      <c r="J177" s="11"/>
-      <c r="K177" s="11" t="s">
+      <c r="J177" s="23"/>
+      <c r="K177" s="23" t="s">
         <v>3399</v>
       </c>
-      <c r="L177" s="13" t="s">
+      <c r="L177" s="25" t="s">
         <v>3401</v>
       </c>
-      <c r="M177" s="14"/>
+      <c r="M177" s="13"/>
       <c r="N177" s="11" t="s">
         <v>2255</v>
       </c>
@@ -19917,7 +19937,7 @@
       <c r="Q177" s="11" t="s">
         <v>3402</v>
       </c>
-      <c r="R177" s="13" t="s">
+      <c r="R177" s="12" t="s">
         <v>3403</v>
       </c>
       <c r="S177" s="11" t="s">
@@ -19947,14 +19967,14 @@
       <c r="H178" s="11" t="s">
         <v>3409</v>
       </c>
-      <c r="I178" s="11" t="s">
+      <c r="I178" s="23" t="s">
         <v>3410</v>
       </c>
-      <c r="J178" s="11"/>
-      <c r="K178" s="11" t="s">
+      <c r="J178" s="23"/>
+      <c r="K178" s="23" t="s">
         <v>3409</v>
       </c>
-      <c r="L178" s="13" t="s">
+      <c r="L178" s="25" t="s">
         <v>3411</v>
       </c>
       <c r="M178" s="11"/>
@@ -19990,14 +20010,14 @@
       <c r="H179" s="11" t="s">
         <v>3415</v>
       </c>
-      <c r="I179" s="11" t="s">
+      <c r="I179" s="23" t="s">
         <v>3416</v>
       </c>
-      <c r="J179" s="11"/>
-      <c r="K179" s="11" t="s">
+      <c r="J179" s="23"/>
+      <c r="K179" s="23" t="s">
         <v>3415</v>
       </c>
-      <c r="L179" s="11"/>
+      <c r="L179" s="23"/>
       <c r="M179" s="11" t="s">
         <v>2383</v>
       </c>
@@ -20037,14 +20057,14 @@
       <c r="H180" s="11" t="s">
         <v>3421</v>
       </c>
-      <c r="I180" s="11" t="s">
+      <c r="I180" s="23" t="s">
         <v>3422</v>
       </c>
-      <c r="J180" s="11"/>
-      <c r="K180" s="11" t="s">
+      <c r="J180" s="23"/>
+      <c r="K180" s="23" t="s">
         <v>3421</v>
       </c>
-      <c r="L180" s="11" t="s">
+      <c r="L180" s="23" t="s">
         <v>3423</v>
       </c>
       <c r="M180" s="11" t="s">
@@ -20082,14 +20102,14 @@
       <c r="H181" s="11" t="s">
         <v>3427</v>
       </c>
-      <c r="I181" s="11" t="s">
+      <c r="I181" s="23" t="s">
         <v>3428</v>
       </c>
-      <c r="J181" s="11"/>
-      <c r="K181" s="11" t="s">
+      <c r="J181" s="23"/>
+      <c r="K181" s="23" t="s">
         <v>3429</v>
       </c>
-      <c r="L181" s="36" t="s">
+      <c r="L181" s="42" t="s">
         <v>3430</v>
       </c>
       <c r="M181" s="11"/>
@@ -20099,11 +20119,11 @@
       <c r="O181" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P181" s="36" t="s">
+      <c r="P181" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q181" s="36"/>
-      <c r="R181" s="36"/>
+      <c r="Q181" s="20"/>
+      <c r="R181" s="20"/>
       <c r="S181" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20131,28 +20151,28 @@
       <c r="H182" s="11" t="s">
         <v>3436</v>
       </c>
-      <c r="I182" s="11" t="s">
+      <c r="I182" s="23" t="s">
         <v>3437</v>
       </c>
-      <c r="J182" s="11"/>
-      <c r="K182" s="11" t="s">
+      <c r="J182" s="23"/>
+      <c r="K182" s="23" t="s">
         <v>3438</v>
       </c>
-      <c r="L182" s="36" t="s">
+      <c r="L182" s="42" t="s">
         <v>3439</v>
       </c>
-      <c r="M182" s="36"/>
+      <c r="M182" s="20"/>
       <c r="N182" s="11" t="s">
         <v>2255</v>
       </c>
       <c r="O182" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P182" s="36" t="s">
+      <c r="P182" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q182" s="36"/>
-      <c r="R182" s="36"/>
+      <c r="Q182" s="20"/>
+      <c r="R182" s="20"/>
       <c r="S182" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20180,14 +20200,14 @@
       <c r="H183" s="11" t="s">
         <v>3443</v>
       </c>
-      <c r="I183" s="11" t="s">
+      <c r="I183" s="23" t="s">
         <v>3428</v>
       </c>
-      <c r="J183" s="11"/>
-      <c r="K183" s="11" t="s">
+      <c r="J183" s="23"/>
+      <c r="K183" s="23" t="s">
         <v>3429</v>
       </c>
-      <c r="L183" s="36" t="s">
+      <c r="L183" s="42" t="s">
         <v>3430</v>
       </c>
       <c r="M183" s="11"/>
@@ -20197,11 +20217,11 @@
       <c r="O183" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P183" s="36" t="s">
+      <c r="P183" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q183" s="36"/>
-      <c r="R183" s="36"/>
+      <c r="Q183" s="20"/>
+      <c r="R183" s="20"/>
       <c r="S183" s="11" t="s">
         <v>3444</v>
       </c>
@@ -20229,14 +20249,14 @@
       <c r="H184" s="11" t="s">
         <v>3447</v>
       </c>
-      <c r="I184" s="11" t="s">
+      <c r="I184" s="23" t="s">
         <v>3428</v>
       </c>
-      <c r="J184" s="11"/>
-      <c r="K184" s="11" t="s">
+      <c r="J184" s="23"/>
+      <c r="K184" s="23" t="s">
         <v>3429</v>
       </c>
-      <c r="L184" s="36" t="s">
+      <c r="L184" s="42" t="s">
         <v>3430</v>
       </c>
       <c r="M184" s="11"/>
@@ -20246,11 +20266,11 @@
       <c r="O184" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P184" s="36" t="s">
+      <c r="P184" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q184" s="36"/>
-      <c r="R184" s="36"/>
+      <c r="Q184" s="20"/>
+      <c r="R184" s="20"/>
       <c r="S184" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20278,14 +20298,14 @@
       <c r="H185" s="11" t="s">
         <v>3451</v>
       </c>
-      <c r="I185" s="11" t="s">
+      <c r="I185" s="23" t="s">
         <v>3428</v>
       </c>
-      <c r="J185" s="11"/>
-      <c r="K185" s="11" t="s">
+      <c r="J185" s="23"/>
+      <c r="K185" s="23" t="s">
         <v>3429</v>
       </c>
-      <c r="L185" s="36" t="s">
+      <c r="L185" s="42" t="s">
         <v>3430</v>
       </c>
       <c r="M185" s="11"/>
@@ -20295,11 +20315,11 @@
       <c r="O185" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P185" s="36" t="s">
+      <c r="P185" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q185" s="36"/>
-      <c r="R185" s="36"/>
+      <c r="Q185" s="20"/>
+      <c r="R185" s="20"/>
       <c r="S185" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20327,14 +20347,14 @@
       <c r="H186" s="11" t="s">
         <v>3456</v>
       </c>
-      <c r="I186" s="11" t="s">
+      <c r="I186" s="23" t="s">
         <v>3428</v>
       </c>
-      <c r="J186" s="11"/>
-      <c r="K186" s="11" t="s">
+      <c r="J186" s="23"/>
+      <c r="K186" s="23" t="s">
         <v>3429</v>
       </c>
-      <c r="L186" s="13" t="s">
+      <c r="L186" s="25" t="s">
         <v>3430</v>
       </c>
       <c r="M186" s="11"/>
@@ -20344,11 +20364,11 @@
       <c r="O186" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P186" s="36" t="s">
+      <c r="P186" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q186" s="36"/>
-      <c r="R186" s="36"/>
+      <c r="Q186" s="20"/>
+      <c r="R186" s="20"/>
       <c r="S186" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20376,28 +20396,28 @@
       <c r="H187" s="11" t="s">
         <v>3461</v>
       </c>
-      <c r="I187" s="11" t="s">
+      <c r="I187" s="23" t="s">
         <v>3437</v>
       </c>
-      <c r="J187" s="11"/>
-      <c r="K187" s="11" t="s">
+      <c r="J187" s="23"/>
+      <c r="K187" s="23" t="s">
         <v>3438</v>
       </c>
-      <c r="L187" s="36" t="s">
+      <c r="L187" s="42" t="s">
         <v>3439</v>
       </c>
-      <c r="M187" s="36"/>
+      <c r="M187" s="20"/>
       <c r="N187" s="11" t="s">
         <v>2255</v>
       </c>
       <c r="O187" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P187" s="13" t="s">
+      <c r="P187" s="12" t="s">
         <v>3432</v>
       </c>
-      <c r="Q187" s="37"/>
-      <c r="R187" s="37"/>
+      <c r="Q187" s="21"/>
+      <c r="R187" s="21"/>
       <c r="S187" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20425,14 +20445,14 @@
       <c r="H188" s="11" t="s">
         <v>3465</v>
       </c>
-      <c r="I188" s="11" t="s">
+      <c r="I188" s="23" t="s">
         <v>3437</v>
       </c>
-      <c r="J188" s="11"/>
-      <c r="K188" s="11" t="s">
+      <c r="J188" s="23"/>
+      <c r="K188" s="23" t="s">
         <v>3438</v>
       </c>
-      <c r="L188" s="13" t="s">
+      <c r="L188" s="25" t="s">
         <v>3439</v>
       </c>
       <c r="M188" s="11"/>
@@ -20442,11 +20462,11 @@
       <c r="O188" s="11" t="s">
         <v>3431</v>
       </c>
-      <c r="P188" s="36" t="s">
+      <c r="P188" s="20" t="s">
         <v>3432</v>
       </c>
-      <c r="Q188" s="36"/>
-      <c r="R188" s="36"/>
+      <c r="Q188" s="20"/>
+      <c r="R188" s="20"/>
       <c r="S188" s="11" t="s">
         <v>3433</v>
       </c>
@@ -20473,17 +20493,17 @@
       <c r="G189" s="11" t="s">
         <v>3470</v>
       </c>
-      <c r="H189" s="13" t="s">
+      <c r="H189" s="12" t="s">
         <v>3471</v>
       </c>
-      <c r="I189" s="11" t="s">
+      <c r="I189" s="23" t="s">
         <v>3472</v>
       </c>
-      <c r="J189" s="11"/>
-      <c r="K189" s="11" t="s">
+      <c r="J189" s="23"/>
+      <c r="K189" s="23" t="s">
         <v>3473</v>
       </c>
-      <c r="L189" s="11" t="s">
+      <c r="L189" s="23" t="s">
         <v>3474</v>
       </c>
       <c r="M189" s="11" t="s">
@@ -20493,11 +20513,11 @@
         <v>2255</v>
       </c>
       <c r="O189" s="11"/>
-      <c r="P189" s="13" t="s">
+      <c r="P189" s="12" t="s">
         <v>3475</v>
       </c>
-      <c r="Q189" s="14"/>
-      <c r="R189" s="14"/>
+      <c r="Q189" s="13"/>
+      <c r="R189" s="13"/>
       <c r="S189" s="11" t="s">
         <v>3476</v>
       </c>
@@ -20525,14 +20545,14 @@
       <c r="H190" s="11" t="s">
         <v>3479</v>
       </c>
-      <c r="I190" s="11" t="s">
+      <c r="I190" s="23" t="s">
         <v>3480</v>
       </c>
-      <c r="J190" s="11"/>
-      <c r="K190" s="11" t="s">
+      <c r="J190" s="23"/>
+      <c r="K190" s="23" t="s">
         <v>3481</v>
       </c>
-      <c r="L190" s="11" t="s">
+      <c r="L190" s="23" t="s">
         <v>3482</v>
       </c>
       <c r="M190" s="11" t="s">
@@ -20574,16 +20594,16 @@
       <c r="H191" s="11" t="s">
         <v>3489</v>
       </c>
-      <c r="I191" s="11" t="s">
+      <c r="I191" s="23" t="s">
         <v>3490</v>
       </c>
-      <c r="J191" s="11" t="s">
+      <c r="J191" s="23" t="s">
         <v>3491</v>
       </c>
-      <c r="K191" s="11" t="s">
+      <c r="K191" s="23" t="s">
         <v>3492</v>
       </c>
-      <c r="L191" s="13" t="s">
+      <c r="L191" s="25" t="s">
         <v>3493</v>
       </c>
       <c r="M191" s="11" t="s">
@@ -20623,14 +20643,14 @@
       <c r="H192" s="11" t="s">
         <v>3499</v>
       </c>
-      <c r="I192" s="11" t="s">
+      <c r="I192" s="23" t="s">
         <v>3480</v>
       </c>
-      <c r="J192" s="11"/>
-      <c r="K192" s="11" t="s">
+      <c r="J192" s="23"/>
+      <c r="K192" s="23" t="s">
         <v>3481</v>
       </c>
-      <c r="L192" s="11" t="s">
+      <c r="L192" s="23" t="s">
         <v>3482</v>
       </c>
       <c r="M192" s="11" t="s">
@@ -20670,14 +20690,14 @@
       <c r="H193" s="11" t="s">
         <v>3504</v>
       </c>
-      <c r="I193" s="11" t="s">
+      <c r="I193" s="23" t="s">
         <v>3505</v>
       </c>
-      <c r="J193" s="11"/>
-      <c r="K193" s="11" t="s">
+      <c r="J193" s="23"/>
+      <c r="K193" s="23" t="s">
         <v>3506</v>
       </c>
-      <c r="L193" s="11" t="s">
+      <c r="L193" s="23" t="s">
         <v>3507</v>
       </c>
       <c r="M193" s="11" t="s">
@@ -20689,11 +20709,11 @@
       <c r="O193" s="11" t="s">
         <v>3508</v>
       </c>
-      <c r="P193" s="13" t="s">
+      <c r="P193" s="12" t="s">
         <v>3509</v>
       </c>
-      <c r="Q193" s="14"/>
-      <c r="R193" s="14"/>
+      <c r="Q193" s="13"/>
+      <c r="R193" s="13"/>
       <c r="S193" s="11" t="s">
         <v>3510</v>
       </c>
@@ -20723,16 +20743,16 @@
       <c r="H194" s="11" t="s">
         <v>3489</v>
       </c>
-      <c r="I194" s="11" t="s">
+      <c r="I194" s="23" t="s">
         <v>3490</v>
       </c>
-      <c r="J194" s="11" t="s">
+      <c r="J194" s="23" t="s">
         <v>3491</v>
       </c>
-      <c r="K194" s="11" t="s">
+      <c r="K194" s="23" t="s">
         <v>3492</v>
       </c>
-      <c r="L194" s="13" t="s">
+      <c r="L194" s="25" t="s">
         <v>3493</v>
       </c>
       <c r="M194" s="11" t="s">
@@ -20772,14 +20792,14 @@
       <c r="H195" s="11" t="s">
         <v>3518</v>
       </c>
-      <c r="I195" s="11" t="s">
+      <c r="I195" s="23" t="s">
         <v>3519</v>
       </c>
-      <c r="J195" s="11"/>
-      <c r="K195" s="11" t="s">
+      <c r="J195" s="23"/>
+      <c r="K195" s="23" t="s">
         <v>3520</v>
       </c>
-      <c r="L195" s="13" t="s">
+      <c r="L195" s="25" t="s">
         <v>3521</v>
       </c>
       <c r="M195" s="11" t="s">
@@ -20821,14 +20841,14 @@
       <c r="H196" s="11" t="s">
         <v>3526</v>
       </c>
-      <c r="I196" s="11" t="s">
+      <c r="I196" s="23" t="s">
         <v>3519</v>
       </c>
-      <c r="J196" s="11"/>
-      <c r="K196" s="11" t="s">
+      <c r="J196" s="23"/>
+      <c r="K196" s="23" t="s">
         <v>3520</v>
       </c>
-      <c r="L196" s="13" t="s">
+      <c r="L196" s="25" t="s">
         <v>3521</v>
       </c>
       <c r="M196" s="11" t="s">
@@ -20870,16 +20890,16 @@
       <c r="H197" s="11" t="s">
         <v>3533</v>
       </c>
-      <c r="I197" s="11" t="s">
+      <c r="I197" s="23" t="s">
         <v>3534</v>
       </c>
-      <c r="J197" s="11" t="s">
+      <c r="J197" s="23" t="s">
         <v>2683</v>
       </c>
-      <c r="K197" s="11" t="s">
+      <c r="K197" s="23" t="s">
         <v>3535</v>
       </c>
-      <c r="L197" s="13" t="s">
+      <c r="L197" s="25" t="s">
         <v>3536</v>
       </c>
       <c r="M197" s="11" t="s">
@@ -20913,14 +20933,14 @@
       </c>
       <c r="G198" s="11"/>
       <c r="H198" s="11"/>
-      <c r="I198" s="11" t="s">
+      <c r="I198" s="23" t="s">
         <v>3540</v>
       </c>
-      <c r="J198" s="11"/>
-      <c r="K198" s="11" t="s">
+      <c r="J198" s="23"/>
+      <c r="K198" s="23" t="s">
         <v>3541</v>
       </c>
-      <c r="L198" s="11" t="s">
+      <c r="L198" s="23" t="s">
         <v>3542</v>
       </c>
       <c r="M198" s="11" t="s">
@@ -20962,16 +20982,16 @@
       <c r="H199" s="11" t="s">
         <v>3549</v>
       </c>
-      <c r="I199" s="11" t="s">
+      <c r="I199" s="23" t="s">
         <v>3550</v>
       </c>
-      <c r="J199" s="11" t="s">
+      <c r="J199" s="23" t="s">
         <v>2683</v>
       </c>
-      <c r="K199" s="11" t="s">
+      <c r="K199" s="23" t="s">
         <v>3551</v>
       </c>
-      <c r="L199" s="11" t="s">
+      <c r="L199" s="23" t="s">
         <v>3552</v>
       </c>
       <c r="M199" s="11" t="s">
@@ -21015,16 +21035,16 @@
       <c r="H200" s="11" t="s">
         <v>3559</v>
       </c>
-      <c r="I200" s="11" t="s">
+      <c r="I200" s="23" t="s">
         <v>3534</v>
       </c>
-      <c r="J200" s="11" t="s">
+      <c r="J200" s="23" t="s">
         <v>2683</v>
       </c>
-      <c r="K200" s="11" t="s">
+      <c r="K200" s="23" t="s">
         <v>3535</v>
       </c>
-      <c r="L200" s="11" t="s">
+      <c r="L200" s="23" t="s">
         <v>3536</v>
       </c>
       <c r="M200" s="11" t="s">
@@ -21064,16 +21084,16 @@
       <c r="H201" s="11" t="s">
         <v>3563</v>
       </c>
-      <c r="I201" s="11" t="s">
+      <c r="I201" s="23" t="s">
         <v>3550</v>
       </c>
-      <c r="J201" s="11" t="s">
+      <c r="J201" s="23" t="s">
         <v>2683</v>
       </c>
-      <c r="K201" s="11" t="s">
+      <c r="K201" s="23" t="s">
         <v>3551</v>
       </c>
-      <c r="L201" s="11" t="s">
+      <c r="L201" s="23" t="s">
         <v>3552</v>
       </c>
       <c r="M201" s="11" t="s">
@@ -21085,11 +21105,11 @@
       <c r="O201" s="11" t="s">
         <v>3564</v>
       </c>
-      <c r="P201" s="13" t="s">
+      <c r="P201" s="12" t="s">
         <v>3565</v>
       </c>
-      <c r="Q201" s="14"/>
-      <c r="R201" s="14"/>
+      <c r="Q201" s="13"/>
+      <c r="R201" s="13"/>
       <c r="S201" s="11" t="s">
         <v>3555</v>
       </c>
@@ -21119,14 +21139,14 @@
       <c r="H202" s="11" t="s">
         <v>3570</v>
       </c>
-      <c r="I202" s="11" t="s">
+      <c r="I202" s="23" t="s">
         <v>3571</v>
       </c>
-      <c r="J202" s="11"/>
-      <c r="K202" s="11" t="s">
+      <c r="J202" s="23"/>
+      <c r="K202" s="23" t="s">
         <v>3572</v>
       </c>
-      <c r="L202" s="11" t="s">
+      <c r="L202" s="23" t="s">
         <v>3573</v>
       </c>
       <c r="M202" s="11"/>
@@ -43855,15 +43875,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="70a4a365-2753-4199-abdb-eb8db1d4debc" xsi:nil="true"/>
@@ -43874,7 +43885,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001DBCBF14208C5B4D9DCB8B0E4F0A424D" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="665055633ffa4ea1ceac9e0b1b8aff7b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d5900feb-dde0-410c-80b8-c2962e8eda82" xmlns:ns3="70a4a365-2753-4199-abdb-eb8db1d4debc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff70244a2ec93a669e69735a2af1e1ac" ns2:_="" ns3:_="">
     <xsd:import namespace="d5900feb-dde0-410c-80b8-c2962e8eda82"/>
@@ -44075,32 +44086,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{306E654B-0A5B-4952-9899-8BE4291BD587}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6E6D350-6E25-477B-B5DC-469D63AF66EF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="70a4a365-2753-4199-abdb-eb8db1d4debc"/>
     <ds:schemaRef ds:uri="d5900feb-dde0-410c-80b8-c2962e8eda82"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E902C50-8F83-4A3A-9ADC-CE38A8CCE144}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -44117,4 +44129,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{306E654B-0A5B-4952-9899-8BE4291BD587}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>